--- a/Toxic Comment Moderation Dataset.xlsx
+++ b/Toxic Comment Moderation Dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Suresh Drive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDC909A-3626-4549-8A87-53018CEF8273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E088C617-7B04-494B-9C82-765F57C44BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="16457" windowHeight="8537" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3103,24 +3103,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW1051"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="48" width="8.88671875" style="1"/>
-    <col min="49" max="49" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="11.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.4609375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.84375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="48" width="8.84375" style="1"/>
+    <col min="49" max="49" width="11.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="AW2" s="2"/>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AW3" s="2"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AW4" s="2"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="AW5" s="2"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AW6" s="2"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AW7" s="2"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AW8" s="2"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="AW9" s="2"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AW10" s="2"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AW11" s="2"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AW12" s="2"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AW13" s="2"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AW14" s="2"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AW15" s="2"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AW16" s="2"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AW17" s="2"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AW18" s="2"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AW19" s="2"/>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AW20" s="2"/>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AW21" s="2"/>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AW22" s="2"/>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AW23" s="2"/>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="AW24" s="2"/>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AW25" s="2"/>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AW26" s="2"/>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AW27" s="2"/>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AW28" s="2"/>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AW29" s="2"/>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="AW30" s="2"/>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AW31" s="2"/>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="AW32" s="2"/>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="AW33" s="2"/>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AW34" s="2"/>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AW35" s="2"/>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AW36" s="2"/>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AW37" s="2"/>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="AW38" s="2"/>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="AW39" s="2"/>
     </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AW40" s="2"/>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AW41" s="2"/>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="AW42" s="2"/>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AW43" s="2"/>
     </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="AW44" s="2"/>
     </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW45" s="2"/>
     </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AW46" s="2"/>
     </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AW47" s="2"/>
     </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AW48" s="2"/>
     </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AW49" s="2"/>
     </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AW50" s="2"/>
     </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="AW51" s="2"/>
     </row>
-    <row r="52" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="AW52" s="2"/>
     </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AW53" s="2"/>
     </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AW54" s="2"/>
     </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AW55" s="2"/>
     </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AW56" s="2"/>
     </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="AW57" s="2"/>
     </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AW58" s="2"/>
     </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AW59" s="2"/>
     </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AW60" s="2"/>
     </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AW61" s="2"/>
     </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="AW62" s="2"/>
     </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="AW63" s="2"/>
     </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AW64" s="2"/>
     </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="AW65" s="2"/>
     </row>
-    <row r="66" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AW66" s="2"/>
     </row>
-    <row r="67" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AW67" s="2"/>
     </row>
-    <row r="68" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AW68" s="2"/>
     </row>
-    <row r="69" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AW69" s="2"/>
     </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AW70" s="2"/>
     </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AW71" s="2"/>
     </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AW72" s="2"/>
     </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="AW73" s="2"/>
     </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="AW74" s="2"/>
     </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AW75" s="2"/>
     </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AW76" s="2"/>
     </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="AW77" s="2"/>
     </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AW78" s="2"/>
     </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="AW79" s="2"/>
     </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AW80" s="2"/>
     </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AW81" s="2"/>
     </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="AW82" s="2"/>
     </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="AW83" s="2"/>
     </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AW84" s="2"/>
     </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AW85" s="2"/>
     </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="AW86" s="2"/>
     </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AW87" s="2"/>
     </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AW88" s="2"/>
     </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AW89" s="2"/>
     </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="AW90" s="2"/>
     </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="AW91" s="2"/>
     </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="AW92" s="2"/>
     </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AW93" s="2"/>
     </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="AW94" s="2"/>
     </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AW95" s="2"/>
     </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AW96" s="2"/>
     </row>
-    <row r="97" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AW97" s="2"/>
     </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AW98" s="2"/>
     </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AW99" s="2"/>
     </row>
-    <row r="100" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AW100" s="2"/>
     </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AW101" s="2"/>
     </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="AW102" s="2"/>
     </row>
-    <row r="103" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AW103" s="2"/>
     </row>
-    <row r="104" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="AW104" s="2"/>
     </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AW105" s="2"/>
     </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AW106" s="2"/>
     </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="AW107" s="2"/>
     </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AW108" s="2"/>
     </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AW109" s="2"/>
     </row>
-    <row r="110" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AW110" s="2"/>
     </row>
-    <row r="111" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AW111" s="2"/>
     </row>
-    <row r="112" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="AW112" s="2"/>
     </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AW113" s="2"/>
     </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="AW114" s="2"/>
     </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AW115" s="2"/>
     </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="AW116" s="2"/>
     </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="AW117" s="2"/>
     </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AW118" s="2"/>
     </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AW119" s="2"/>
     </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AW120" s="2"/>
     </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AW121" s="2"/>
     </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AW122" s="2"/>
     </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="AW123" s="2"/>
     </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AW124" s="2"/>
     </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AW125" s="2"/>
     </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AW126" s="2"/>
     </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AW127" s="2"/>
     </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="AW128" s="2"/>
     </row>
-    <row r="129" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="AW129" s="2"/>
     </row>
-    <row r="130" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AW130" s="2"/>
     </row>
-    <row r="131" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AW131" s="2"/>
     </row>
-    <row r="132" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AW132" s="2"/>
     </row>
-    <row r="133" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="AW133" s="2"/>
     </row>
-    <row r="134" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="AW134" s="2"/>
     </row>
-    <row r="135" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="AW135" s="2"/>
     </row>
-    <row r="136" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="AW136" s="2"/>
     </row>
-    <row r="137" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="AW137" s="2"/>
     </row>
-    <row r="138" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="AW138" s="2"/>
     </row>
-    <row r="139" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AW139" s="2"/>
     </row>
-    <row r="140" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="AW140" s="2"/>
     </row>
-    <row r="141" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AW141" s="2"/>
     </row>
-    <row r="142" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AW142" s="2"/>
     </row>
-    <row r="143" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="AW143" s="2"/>
     </row>
-    <row r="144" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="AW144" s="2"/>
     </row>
-    <row r="145" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AW145" s="2"/>
     </row>
-    <row r="146" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AW146" s="2"/>
     </row>
-    <row r="147" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AW147" s="2"/>
     </row>
-    <row r="148" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AW148" s="2"/>
     </row>
-    <row r="149" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="AW149" s="2"/>
     </row>
-    <row r="150" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AW150" s="2"/>
     </row>
-    <row r="151" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="AW151" s="2"/>
     </row>
-    <row r="152" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="AW152" s="2"/>
     </row>
-    <row r="153" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AW153" s="2"/>
     </row>
-    <row r="154" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="AW154" s="2"/>
     </row>
-    <row r="155" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AW155" s="2"/>
     </row>
-    <row r="156" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="AW156" s="2"/>
     </row>
-    <row r="157" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AW157" s="2"/>
     </row>
-    <row r="158" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="AW158" s="2"/>
     </row>
-    <row r="159" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="AW159" s="2"/>
     </row>
-    <row r="160" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AW160" s="2"/>
     </row>
-    <row r="161" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AW161" s="2"/>
     </row>
-    <row r="162" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="AW162" s="2"/>
     </row>
-    <row r="163" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="AW163" s="2"/>
     </row>
-    <row r="164" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="AW164" s="2"/>
     </row>
-    <row r="165" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="AW165" s="2"/>
     </row>
-    <row r="166" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="AW166" s="2"/>
     </row>
-    <row r="167" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AW167" s="2"/>
     </row>
-    <row r="168" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AW168" s="2"/>
     </row>
-    <row r="169" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AW169" s="2"/>
     </row>
-    <row r="170" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="AW170" s="2"/>
     </row>
-    <row r="171" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="AW171" s="2"/>
     </row>
-    <row r="172" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AW172" s="2"/>
     </row>
-    <row r="173" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AW173" s="2"/>
     </row>
-    <row r="174" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AW174" s="2"/>
     </row>
-    <row r="175" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AW175" s="2"/>
     </row>
-    <row r="176" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="AW176" s="2"/>
     </row>
-    <row r="177" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AW177" s="2"/>
     </row>
-    <row r="178" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="AW178" s="2"/>
     </row>
-    <row r="179" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AW179" s="2"/>
     </row>
-    <row r="180" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AW180" s="2"/>
     </row>
-    <row r="181" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="AW181" s="2"/>
     </row>
-    <row r="182" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="AW182" s="2"/>
     </row>
-    <row r="183" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="AW183" s="2"/>
     </row>
-    <row r="184" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="AW184" s="2"/>
     </row>
-    <row r="185" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="AW185" s="2"/>
     </row>
-    <row r="186" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="AW186" s="2"/>
     </row>
-    <row r="187" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="AW187" s="2"/>
     </row>
-    <row r="188" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AW188" s="2"/>
     </row>
-    <row r="189" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="AW189" s="2"/>
     </row>
-    <row r="190" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AW190" s="2"/>
     </row>
-    <row r="191" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AW191" s="2"/>
     </row>
-    <row r="192" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="AW192" s="2"/>
     </row>
-    <row r="193" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="AW193" s="2"/>
     </row>
-    <row r="194" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AW194" s="2"/>
     </row>
-    <row r="195" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AW195" s="2"/>
     </row>
-    <row r="196" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AW196" s="2"/>
     </row>
-    <row r="197" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="AW197" s="2"/>
     </row>
-    <row r="198" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="AW198" s="2"/>
     </row>
-    <row r="199" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="AW199" s="2"/>
     </row>
-    <row r="200" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="AW200" s="2"/>
     </row>
-    <row r="201" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AW201" s="2"/>
     </row>
-    <row r="202" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AW202" s="2"/>
     </row>
-    <row r="203" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AW203" s="2"/>
     </row>
-    <row r="204" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AW204" s="2"/>
     </row>
-    <row r="205" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="AW205" s="2"/>
     </row>
-    <row r="206" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="AW206" s="2"/>
     </row>
-    <row r="207" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="AW207" s="2"/>
     </row>
-    <row r="208" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="AW208" s="2"/>
     </row>
-    <row r="209" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="AW209" s="2"/>
     </row>
-    <row r="210" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AW210" s="2"/>
     </row>
-    <row r="211" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="AW211" s="2"/>
     </row>
-    <row r="212" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="AW212" s="2"/>
     </row>
-    <row r="213" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AW213" s="2"/>
     </row>
-    <row r="214" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AW214" s="2"/>
     </row>
-    <row r="215" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="AW215" s="2"/>
     </row>
-    <row r="216" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AW216" s="2"/>
     </row>
-    <row r="217" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="AW217" s="2"/>
     </row>
-    <row r="218" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AW218" s="2"/>
     </row>
-    <row r="219" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AW219" s="2"/>
     </row>
-    <row r="220" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="AW220" s="2"/>
     </row>
-    <row r="221" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="AW221" s="2"/>
     </row>
-    <row r="222" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AW222" s="2"/>
     </row>
-    <row r="223" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="AW223" s="2"/>
     </row>
-    <row r="224" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="AW224" s="2"/>
     </row>
-    <row r="225" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="AW225" s="2"/>
     </row>
-    <row r="226" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="AW226" s="2"/>
     </row>
-    <row r="227" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AW227" s="2"/>
     </row>
-    <row r="228" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AW228" s="2"/>
     </row>
-    <row r="229" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="AW229" s="2"/>
     </row>
-    <row r="230" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AW230" s="2"/>
     </row>
-    <row r="231" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AW231" s="2"/>
     </row>
-    <row r="232" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AW232" s="2"/>
     </row>
-    <row r="233" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AW233" s="2"/>
     </row>
-    <row r="234" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="AW234" s="2"/>
     </row>
-    <row r="235" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="AW235" s="2"/>
     </row>
-    <row r="236" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="AW236" s="2"/>
     </row>
-    <row r="237" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="AW237" s="2"/>
     </row>
-    <row r="238" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AW238" s="2"/>
     </row>
-    <row r="239" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="AW239" s="2"/>
     </row>
-    <row r="240" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AW240" s="2"/>
     </row>
-    <row r="241" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AW241" s="2"/>
     </row>
-    <row r="242" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="AW242" s="2"/>
     </row>
-    <row r="243" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="AW243" s="2"/>
     </row>
-    <row r="244" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AW244" s="2"/>
     </row>
-    <row r="245" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="AW245" s="2"/>
     </row>
-    <row r="246" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="AW246" s="2"/>
     </row>
-    <row r="247" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AW247" s="2"/>
     </row>
-    <row r="248" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="AW248" s="2"/>
     </row>
-    <row r="249" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="AW249" s="2"/>
     </row>
-    <row r="250" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AW250" s="2"/>
     </row>
-    <row r="251" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="AW251" s="2"/>
     </row>
-    <row r="252" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A252" s="1">
         <v>251</v>
       </c>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="AW252" s="2"/>
     </row>
-    <row r="253" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="AW253" s="2"/>
     </row>
-    <row r="254" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="AW254" s="2"/>
     </row>
-    <row r="255" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AW255" s="2"/>
     </row>
-    <row r="256" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="AW256" s="2"/>
     </row>
-    <row r="257" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="AW257" s="2"/>
     </row>
-    <row r="258" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AW258" s="2"/>
     </row>
-    <row r="259" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A259" s="1">
         <v>258</v>
       </c>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AW259" s="2"/>
     </row>
-    <row r="260" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A260" s="1">
         <v>259</v>
       </c>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="AW260" s="2"/>
     </row>
-    <row r="261" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A261" s="1">
         <v>260</v>
       </c>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="AW261" s="2"/>
     </row>
-    <row r="262" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A262" s="1">
         <v>261</v>
       </c>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AW262" s="2"/>
     </row>
-    <row r="263" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="AW263" s="2"/>
     </row>
-    <row r="264" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A264" s="1">
         <v>263</v>
       </c>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="AW264" s="2"/>
     </row>
-    <row r="265" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A265" s="1">
         <v>264</v>
       </c>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AW265" s="2"/>
     </row>
-    <row r="266" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A266" s="1">
         <v>265</v>
       </c>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="AW266" s="2"/>
     </row>
-    <row r="267" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A267" s="1">
         <v>266</v>
       </c>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="AW267" s="2"/>
     </row>
-    <row r="268" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="AW268" s="2"/>
     </row>
-    <row r="269" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A269" s="1">
         <v>268</v>
       </c>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="AW269" s="2"/>
     </row>
-    <row r="270" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A270" s="1">
         <v>269</v>
       </c>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="AW270" s="2"/>
     </row>
-    <row r="271" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A271" s="1">
         <v>270</v>
       </c>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AW271" s="2"/>
     </row>
-    <row r="272" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A272" s="1">
         <v>271</v>
       </c>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="AW272" s="2"/>
     </row>
-    <row r="273" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AW273" s="2"/>
     </row>
-    <row r="274" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A274" s="1">
         <v>273</v>
       </c>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="AW274" s="2"/>
     </row>
-    <row r="275" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A275" s="1">
         <v>274</v>
       </c>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="AW275" s="2"/>
     </row>
-    <row r="276" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A276" s="1">
         <v>275</v>
       </c>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="AW276" s="2"/>
     </row>
-    <row r="277" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A277" s="1">
         <v>276</v>
       </c>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="AW277" s="2"/>
     </row>
-    <row r="278" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AW278" s="2"/>
     </row>
-    <row r="279" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A279" s="1">
         <v>278</v>
       </c>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="AW279" s="2"/>
     </row>
-    <row r="280" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A280" s="1">
         <v>279</v>
       </c>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="AW280" s="2"/>
     </row>
-    <row r="281" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A281" s="1">
         <v>280</v>
       </c>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AW281" s="2"/>
     </row>
-    <row r="282" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A282" s="1">
         <v>281</v>
       </c>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="AW282" s="2"/>
     </row>
-    <row r="283" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A283" s="1">
         <v>282</v>
       </c>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AW283" s="2"/>
     </row>
-    <row r="284" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A284" s="1">
         <v>283</v>
       </c>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="AW284" s="2"/>
     </row>
-    <row r="285" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A285" s="1">
         <v>284</v>
       </c>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="AW285" s="2"/>
     </row>
-    <row r="286" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A286" s="1">
         <v>285</v>
       </c>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AW286" s="2"/>
     </row>
-    <row r="287" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A287" s="1">
         <v>286</v>
       </c>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="AW287" s="2"/>
     </row>
-    <row r="288" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A288" s="1">
         <v>287</v>
       </c>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="AW288" s="2"/>
     </row>
-    <row r="289" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A289" s="1">
         <v>288</v>
       </c>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="AW289" s="2"/>
     </row>
-    <row r="290" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A290" s="1">
         <v>289</v>
       </c>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="AW290" s="2"/>
     </row>
-    <row r="291" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A291" s="1">
         <v>290</v>
       </c>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="AW291" s="2"/>
     </row>
-    <row r="292" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A292" s="1">
         <v>291</v>
       </c>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="AW292" s="2"/>
     </row>
-    <row r="293" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AW293" s="2"/>
     </row>
-    <row r="294" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A294" s="1">
         <v>293</v>
       </c>
@@ -12821,7 +12821,7 @@
       </c>
       <c r="AW294" s="2"/>
     </row>
-    <row r="295" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A295" s="1">
         <v>294</v>
       </c>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="AW295" s="2"/>
     </row>
-    <row r="296" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A296" s="1">
         <v>295</v>
       </c>
@@ -12887,7 +12887,7 @@
       </c>
       <c r="AW296" s="2"/>
     </row>
-    <row r="297" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A297" s="1">
         <v>296</v>
       </c>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="AW297" s="2"/>
     </row>
-    <row r="298" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A298" s="1">
         <v>297</v>
       </c>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="AW298" s="2"/>
     </row>
-    <row r="299" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A299" s="1">
         <v>298</v>
       </c>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="AW299" s="2"/>
     </row>
-    <row r="300" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A300" s="1">
         <v>299</v>
       </c>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="AW300" s="2"/>
     </row>
-    <row r="301" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A301" s="1">
         <v>300</v>
       </c>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="AW301" s="2"/>
     </row>
-    <row r="302" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A302" s="1">
         <v>301</v>
       </c>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="AW302" s="2"/>
     </row>
-    <row r="303" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A303" s="1">
         <v>302</v>
       </c>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="AW303" s="2"/>
     </row>
-    <row r="304" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A304" s="1">
         <v>303</v>
       </c>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="AW304" s="2"/>
     </row>
-    <row r="305" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A305" s="1">
         <v>304</v>
       </c>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AW305" s="2"/>
     </row>
-    <row r="306" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A306" s="1">
         <v>305</v>
       </c>
@@ -13217,7 +13217,7 @@
       </c>
       <c r="AW306" s="2"/>
     </row>
-    <row r="307" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A307" s="1">
         <v>306</v>
       </c>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="AW307" s="2"/>
     </row>
-    <row r="308" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A308" s="1">
         <v>307</v>
       </c>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="AW308" s="2"/>
     </row>
-    <row r="309" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A309" s="1">
         <v>308</v>
       </c>
@@ -13316,7 +13316,7 @@
       </c>
       <c r="AW309" s="2"/>
     </row>
-    <row r="310" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A310" s="1">
         <v>309</v>
       </c>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AW310" s="2"/>
     </row>
-    <row r="311" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A311" s="1">
         <v>310</v>
       </c>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AW311" s="2"/>
     </row>
-    <row r="312" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A312" s="1">
         <v>311</v>
       </c>
@@ -13415,7 +13415,7 @@
       </c>
       <c r="AW312" s="2"/>
     </row>
-    <row r="313" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A313" s="1">
         <v>312</v>
       </c>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="AW313" s="2"/>
     </row>
-    <row r="314" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A314" s="1">
         <v>313</v>
       </c>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="AW314" s="2"/>
     </row>
-    <row r="315" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A315" s="1">
         <v>314</v>
       </c>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="AW315" s="2"/>
     </row>
-    <row r="316" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A316" s="1">
         <v>315</v>
       </c>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="AW316" s="2"/>
     </row>
-    <row r="317" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A317" s="1">
         <v>316</v>
       </c>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AW317" s="2"/>
     </row>
-    <row r="318" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A318" s="1">
         <v>317</v>
       </c>
@@ -13613,7 +13613,7 @@
       </c>
       <c r="AW318" s="2"/>
     </row>
-    <row r="319" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A319" s="1">
         <v>318</v>
       </c>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="AW319" s="2"/>
     </row>
-    <row r="320" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A320" s="1">
         <v>319</v>
       </c>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AW320" s="2"/>
     </row>
-    <row r="321" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A321" s="1">
         <v>320</v>
       </c>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="AW321" s="2"/>
     </row>
-    <row r="322" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A322" s="1">
         <v>321</v>
       </c>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="AW322" s="2"/>
     </row>
-    <row r="323" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A323" s="1">
         <v>322</v>
       </c>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="AW323" s="2"/>
     </row>
-    <row r="324" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="AW324" s="2"/>
     </row>
-    <row r="325" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A325" s="1">
         <v>324</v>
       </c>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="AW325" s="2"/>
     </row>
-    <row r="326" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A326" s="1">
         <v>325</v>
       </c>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AW326" s="2"/>
     </row>
-    <row r="327" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A327" s="1">
         <v>326</v>
       </c>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="AW327" s="2"/>
     </row>
-    <row r="328" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A328" s="1">
         <v>327</v>
       </c>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="AW328" s="2"/>
     </row>
-    <row r="329" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="AW329" s="2"/>
     </row>
-    <row r="330" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A330" s="1">
         <v>329</v>
       </c>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="AW330" s="2"/>
     </row>
-    <row r="331" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A331" s="1">
         <v>330</v>
       </c>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="AW331" s="2"/>
     </row>
-    <row r="332" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A332" s="1">
         <v>331</v>
       </c>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="AW332" s="2"/>
     </row>
-    <row r="333" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A333" s="1">
         <v>332</v>
       </c>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AW333" s="2"/>
     </row>
-    <row r="334" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A334" s="1">
         <v>333</v>
       </c>
@@ -14141,7 +14141,7 @@
       </c>
       <c r="AW334" s="2"/>
     </row>
-    <row r="335" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AW335" s="2"/>
     </row>
-    <row r="336" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A336" s="1">
         <v>335</v>
       </c>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="AW336" s="2"/>
     </row>
-    <row r="337" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
         <v>336</v>
       </c>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="AW337" s="2"/>
     </row>
-    <row r="338" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A338" s="1">
         <v>337</v>
       </c>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="AW338" s="2"/>
     </row>
-    <row r="339" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
         <v>338</v>
       </c>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AW339" s="2"/>
     </row>
-    <row r="340" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A340" s="1">
         <v>339</v>
       </c>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="AW340" s="2"/>
     </row>
-    <row r="341" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>340</v>
       </c>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="AW341" s="2"/>
     </row>
-    <row r="342" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>341</v>
       </c>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="AW342" s="2"/>
     </row>
-    <row r="343" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A343" s="1">
         <v>342</v>
       </c>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AW343" s="2"/>
     </row>
-    <row r="344" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A344" s="1">
         <v>343</v>
       </c>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="AW344" s="2"/>
     </row>
-    <row r="345" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A345" s="1">
         <v>344</v>
       </c>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="AW345" s="2"/>
     </row>
-    <row r="346" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>345</v>
       </c>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="AW346" s="2"/>
     </row>
-    <row r="347" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>346</v>
       </c>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="AW347" s="2"/>
     </row>
-    <row r="348" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>347</v>
       </c>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="AW348" s="2"/>
     </row>
-    <row r="349" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>348</v>
       </c>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="AW349" s="2"/>
     </row>
-    <row r="350" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>349</v>
       </c>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="AW350" s="2"/>
     </row>
-    <row r="351" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>350</v>
       </c>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="AW351" s="2"/>
     </row>
-    <row r="352" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A352" s="1">
         <v>351</v>
       </c>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="AW352" s="2"/>
     </row>
-    <row r="353" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A353" s="1">
         <v>352</v>
       </c>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="AW353" s="2"/>
     </row>
-    <row r="354" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A354" s="1">
         <v>353</v>
       </c>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="AW354" s="2"/>
     </row>
-    <row r="355" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A355" s="1">
         <v>354</v>
       </c>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="AW355" s="2"/>
     </row>
-    <row r="356" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A356" s="1">
         <v>355</v>
       </c>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AW356" s="2"/>
     </row>
-    <row r="357" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A357" s="1">
         <v>356</v>
       </c>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="AW357" s="2"/>
     </row>
-    <row r="358" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A358" s="1">
         <v>357</v>
       </c>
@@ -14933,7 +14933,7 @@
       </c>
       <c r="AW358" s="2"/>
     </row>
-    <row r="359" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A359" s="1">
         <v>358</v>
       </c>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AW359" s="2"/>
     </row>
-    <row r="360" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A360" s="1">
         <v>359</v>
       </c>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="AW360" s="2"/>
     </row>
-    <row r="361" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A361" s="1">
         <v>360</v>
       </c>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="AW361" s="2"/>
     </row>
-    <row r="362" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A362" s="1">
         <v>361</v>
       </c>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="AW362" s="2"/>
     </row>
-    <row r="363" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="AW363" s="2"/>
     </row>
-    <row r="364" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A364" s="1">
         <v>363</v>
       </c>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="AW364" s="2"/>
     </row>
-    <row r="365" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="AW365" s="2"/>
     </row>
-    <row r="366" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A366" s="1">
         <v>365</v>
       </c>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="AW366" s="2"/>
     </row>
-    <row r="367" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A367" s="1">
         <v>366</v>
       </c>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="AW367" s="2"/>
     </row>
-    <row r="368" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A368" s="1">
         <v>367</v>
       </c>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="AW368" s="2"/>
     </row>
-    <row r="369" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A369" s="1">
         <v>368</v>
       </c>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="AW369" s="2"/>
     </row>
-    <row r="370" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A370" s="1">
         <v>369</v>
       </c>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="AW370" s="2"/>
     </row>
-    <row r="371" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A371" s="1">
         <v>370</v>
       </c>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="AW371" s="2"/>
     </row>
-    <row r="372" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="AW372" s="2"/>
     </row>
-    <row r="373" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A373" s="1">
         <v>372</v>
       </c>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="AW373" s="2"/>
     </row>
-    <row r="374" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A374" s="1">
         <v>373</v>
       </c>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="AW374" s="2"/>
     </row>
-    <row r="375" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A375" s="1">
         <v>374</v>
       </c>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="AW375" s="2"/>
     </row>
-    <row r="376" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A376" s="1">
         <v>375</v>
       </c>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="AW376" s="2"/>
     </row>
-    <row r="377" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A377" s="1">
         <v>376</v>
       </c>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AW377" s="2"/>
     </row>
-    <row r="378" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A378" s="1">
         <v>377</v>
       </c>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AW378" s="2"/>
     </row>
-    <row r="379" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A379" s="1">
         <v>378</v>
       </c>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="AW379" s="2"/>
     </row>
-    <row r="380" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A380" s="1">
         <v>379</v>
       </c>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="AW380" s="2"/>
     </row>
-    <row r="381" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A381" s="1">
         <v>380</v>
       </c>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="AW381" s="2"/>
     </row>
-    <row r="382" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A382" s="1">
         <v>381</v>
       </c>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="AW382" s="2"/>
     </row>
-    <row r="383" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A383" s="1">
         <v>382</v>
       </c>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AW383" s="2"/>
     </row>
-    <row r="384" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A384" s="1">
         <v>383</v>
       </c>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="AW384" s="2"/>
     </row>
-    <row r="385" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A385" s="1">
         <v>384</v>
       </c>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="AW385" s="2"/>
     </row>
-    <row r="386" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A386" s="1">
         <v>385</v>
       </c>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="AW386" s="2"/>
     </row>
-    <row r="387" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A387" s="1">
         <v>386</v>
       </c>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="AW387" s="2"/>
     </row>
-    <row r="388" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A388" s="1">
         <v>387</v>
       </c>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="AW388" s="2"/>
     </row>
-    <row r="389" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A389" s="1">
         <v>388</v>
       </c>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="AW389" s="2"/>
     </row>
-    <row r="390" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A390" s="1">
         <v>389</v>
       </c>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="AW390" s="2"/>
     </row>
-    <row r="391" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A391" s="1">
         <v>390</v>
       </c>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="AW391" s="2"/>
     </row>
-    <row r="392" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A392" s="1">
         <v>391</v>
       </c>
@@ -16055,7 +16055,7 @@
       </c>
       <c r="AW392" s="2"/>
     </row>
-    <row r="393" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A393" s="1">
         <v>392</v>
       </c>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="AW393" s="2"/>
     </row>
-    <row r="394" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A394" s="1">
         <v>393</v>
       </c>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="AW394" s="2"/>
     </row>
-    <row r="395" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A395" s="1">
         <v>394</v>
       </c>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AW395" s="2"/>
     </row>
-    <row r="396" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A396" s="1">
         <v>395</v>
       </c>
@@ -16187,7 +16187,7 @@
       </c>
       <c r="AW396" s="2"/>
     </row>
-    <row r="397" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A397" s="1">
         <v>396</v>
       </c>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="AW397" s="2"/>
     </row>
-    <row r="398" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A398" s="1">
         <v>397</v>
       </c>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AW398" s="2"/>
     </row>
-    <row r="399" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A399" s="1">
         <v>398</v>
       </c>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AW399" s="2"/>
     </row>
-    <row r="400" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A400" s="1">
         <v>399</v>
       </c>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="AW400" s="2"/>
     </row>
-    <row r="401" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A401" s="1">
         <v>400</v>
       </c>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="AW401" s="2"/>
     </row>
-    <row r="402" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A402" s="1">
         <v>401</v>
       </c>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="AW402" s="2"/>
     </row>
-    <row r="403" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A403" s="1">
         <v>402</v>
       </c>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="AW403" s="2"/>
     </row>
-    <row r="404" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -16451,7 +16451,7 @@
       </c>
       <c r="AW404" s="2"/>
     </row>
-    <row r="405" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A405" s="1">
         <v>404</v>
       </c>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="AW405" s="2"/>
     </row>
-    <row r="406" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A406" s="1">
         <v>405</v>
       </c>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="AW406" s="2"/>
     </row>
-    <row r="407" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A407" s="1">
         <v>406</v>
       </c>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AW407" s="2"/>
     </row>
-    <row r="408" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A408" s="1">
         <v>407</v>
       </c>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AW408" s="2"/>
     </row>
-    <row r="409" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A409" s="1">
         <v>408</v>
       </c>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="AW409" s="2"/>
     </row>
-    <row r="410" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A410" s="1">
         <v>409</v>
       </c>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="AW410" s="2"/>
     </row>
-    <row r="411" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A411" s="1">
         <v>410</v>
       </c>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AW411" s="2"/>
     </row>
-    <row r="412" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A412" s="1">
         <v>411</v>
       </c>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AW412" s="2"/>
     </row>
-    <row r="413" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A413" s="1">
         <v>412</v>
       </c>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="AW413" s="2"/>
     </row>
-    <row r="414" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A414" s="1">
         <v>413</v>
       </c>
@@ -16781,7 +16781,7 @@
       </c>
       <c r="AW414" s="2"/>
     </row>
-    <row r="415" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A415" s="1">
         <v>414</v>
       </c>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="AW415" s="2"/>
     </row>
-    <row r="416" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A416" s="1">
         <v>415</v>
       </c>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="AW416" s="2"/>
     </row>
-    <row r="417" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A417" s="1">
         <v>416</v>
       </c>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="AW417" s="2"/>
     </row>
-    <row r="418" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A418" s="1">
         <v>417</v>
       </c>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="AW418" s="2"/>
     </row>
-    <row r="419" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A419" s="1">
         <v>418</v>
       </c>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="AW419" s="2"/>
     </row>
-    <row r="420" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A420" s="1">
         <v>419</v>
       </c>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="AW420" s="2"/>
     </row>
-    <row r="421" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A421" s="1">
         <v>420</v>
       </c>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="AW421" s="2"/>
     </row>
-    <row r="422" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A422" s="1">
         <v>421</v>
       </c>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AW422" s="2"/>
     </row>
-    <row r="423" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A423" s="1">
         <v>422</v>
       </c>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="AW423" s="2"/>
     </row>
-    <row r="424" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A424" s="1">
         <v>423</v>
       </c>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="AW424" s="2"/>
     </row>
-    <row r="425" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A425" s="1">
         <v>424</v>
       </c>
@@ -17144,7 +17144,7 @@
       </c>
       <c r="AW425" s="2"/>
     </row>
-    <row r="426" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A426" s="1">
         <v>425</v>
       </c>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AW426" s="2"/>
     </row>
-    <row r="427" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A427" s="1">
         <v>426</v>
       </c>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="AW427" s="2"/>
     </row>
-    <row r="428" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A428" s="1">
         <v>427</v>
       </c>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="AW428" s="2"/>
     </row>
-    <row r="429" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A429" s="1">
         <v>428</v>
       </c>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="AW429" s="2"/>
     </row>
-    <row r="430" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A430" s="1">
         <v>429</v>
       </c>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="AW430" s="2"/>
     </row>
-    <row r="431" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A431" s="1">
         <v>430</v>
       </c>
@@ -17342,7 +17342,7 @@
       </c>
       <c r="AW431" s="2"/>
     </row>
-    <row r="432" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A432" s="1">
         <v>431</v>
       </c>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="AW432" s="2"/>
     </row>
-    <row r="433" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A433" s="1">
         <v>432</v>
       </c>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="AW433" s="2"/>
     </row>
-    <row r="434" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A434" s="1">
         <v>433</v>
       </c>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="AW434" s="2"/>
     </row>
-    <row r="435" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A435" s="1">
         <v>434</v>
       </c>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="AW435" s="2"/>
     </row>
-    <row r="436" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A436" s="1">
         <v>435</v>
       </c>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AW436" s="2"/>
     </row>
-    <row r="437" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A437" s="1">
         <v>436</v>
       </c>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="AW437" s="2"/>
     </row>
-    <row r="438" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A438" s="1">
         <v>437</v>
       </c>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="AW438" s="2"/>
     </row>
-    <row r="439" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A439" s="1">
         <v>438</v>
       </c>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="AW439" s="2"/>
     </row>
-    <row r="440" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A440" s="1">
         <v>439</v>
       </c>
@@ -17639,7 +17639,7 @@
       </c>
       <c r="AW440" s="2"/>
     </row>
-    <row r="441" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A441" s="1">
         <v>440</v>
       </c>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AW441" s="2"/>
     </row>
-    <row r="442" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A442" s="1">
         <v>441</v>
       </c>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="AW442" s="2"/>
     </row>
-    <row r="443" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A443" s="1">
         <v>442</v>
       </c>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="AW443" s="2"/>
     </row>
-    <row r="444" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A444" s="1">
         <v>443</v>
       </c>
@@ -17771,7 +17771,7 @@
       </c>
       <c r="AW444" s="2"/>
     </row>
-    <row r="445" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A445" s="1">
         <v>444</v>
       </c>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AW445" s="2"/>
     </row>
-    <row r="446" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A446" s="1">
         <v>445</v>
       </c>
@@ -17837,7 +17837,7 @@
       </c>
       <c r="AW446" s="2"/>
     </row>
-    <row r="447" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A447" s="1">
         <v>446</v>
       </c>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AW447" s="2"/>
     </row>
-    <row r="448" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A448" s="1">
         <v>447</v>
       </c>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="AW448" s="2"/>
     </row>
-    <row r="449" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A449" s="1">
         <v>448</v>
       </c>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="AW449" s="2"/>
     </row>
-    <row r="450" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A450" s="1">
         <v>449</v>
       </c>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="AW450" s="2"/>
     </row>
-    <row r="451" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A451" s="1">
         <v>450</v>
       </c>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="AW451" s="2"/>
     </row>
-    <row r="452" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A452" s="1">
         <v>451</v>
       </c>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="AW452" s="2"/>
     </row>
-    <row r="453" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A453" s="1">
         <v>452</v>
       </c>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="AW453" s="2"/>
     </row>
-    <row r="454" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A454" s="1">
         <v>453</v>
       </c>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="AW454" s="2"/>
     </row>
-    <row r="455" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A455" s="1">
         <v>454</v>
       </c>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="AW455" s="2"/>
     </row>
-    <row r="456" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A456" s="1">
         <v>455</v>
       </c>
@@ -18167,7 +18167,7 @@
       </c>
       <c r="AW456" s="2"/>
     </row>
-    <row r="457" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A457" s="1">
         <v>456</v>
       </c>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="AW457" s="2"/>
     </row>
-    <row r="458" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A458" s="1">
         <v>457</v>
       </c>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="AW458" s="2"/>
     </row>
-    <row r="459" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A459" s="1">
         <v>458</v>
       </c>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="AW459" s="2"/>
     </row>
-    <row r="460" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A460" s="1">
         <v>459</v>
       </c>
@@ -18299,7 +18299,7 @@
       </c>
       <c r="AW460" s="2"/>
     </row>
-    <row r="461" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A461" s="1">
         <v>460</v>
       </c>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="AW461" s="2"/>
     </row>
-    <row r="462" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A462" s="1">
         <v>461</v>
       </c>
@@ -18365,7 +18365,7 @@
       </c>
       <c r="AW462" s="2"/>
     </row>
-    <row r="463" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A463" s="1">
         <v>462</v>
       </c>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="AW463" s="2"/>
     </row>
-    <row r="464" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A464" s="1">
         <v>463</v>
       </c>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="AW464" s="2"/>
     </row>
-    <row r="465" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A465" s="1">
         <v>464</v>
       </c>
@@ -18464,7 +18464,7 @@
       </c>
       <c r="AW465" s="2"/>
     </row>
-    <row r="466" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A466" s="1">
         <v>465</v>
       </c>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AW466" s="2"/>
     </row>
-    <row r="467" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A467" s="1">
         <v>466</v>
       </c>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="AW467" s="2"/>
     </row>
-    <row r="468" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A468" s="1">
         <v>467</v>
       </c>
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AW468" s="2"/>
     </row>
-    <row r="469" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A469" s="1">
         <v>468</v>
       </c>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AW469" s="2"/>
     </row>
-    <row r="470" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A470" s="1">
         <v>469</v>
       </c>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="AW470" s="2"/>
     </row>
-    <row r="471" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A471" s="1">
         <v>470</v>
       </c>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="AW471" s="2"/>
     </row>
-    <row r="472" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A472" s="1">
         <v>471</v>
       </c>
@@ -18695,7 +18695,7 @@
       </c>
       <c r="AW472" s="2"/>
     </row>
-    <row r="473" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A473" s="1">
         <v>472</v>
       </c>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="AW473" s="2"/>
     </row>
-    <row r="474" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A474" s="1">
         <v>473</v>
       </c>
@@ -18761,7 +18761,7 @@
       </c>
       <c r="AW474" s="2"/>
     </row>
-    <row r="475" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A475" s="1">
         <v>474</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AW475" s="2"/>
     </row>
-    <row r="476" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A476" s="1">
         <v>475</v>
       </c>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="AW476" s="2"/>
     </row>
-    <row r="477" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A477" s="1">
         <v>476</v>
       </c>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="AW477" s="2"/>
     </row>
-    <row r="478" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A478" s="1">
         <v>477</v>
       </c>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="AW478" s="2"/>
     </row>
-    <row r="479" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A479" s="1">
         <v>478</v>
       </c>
@@ -18926,7 +18926,7 @@
       </c>
       <c r="AW479" s="2"/>
     </row>
-    <row r="480" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A480" s="1">
         <v>479</v>
       </c>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="AW480" s="2"/>
     </row>
-    <row r="481" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A481" s="1">
         <v>480</v>
       </c>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="AW481" s="2"/>
     </row>
-    <row r="482" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A482" s="1">
         <v>481</v>
       </c>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="AW482" s="2"/>
     </row>
-    <row r="483" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A483" s="1">
         <v>482</v>
       </c>
@@ -19058,7 +19058,7 @@
       </c>
       <c r="AW483" s="2"/>
     </row>
-    <row r="484" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A484" s="1">
         <v>483</v>
       </c>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="AW484" s="2"/>
     </row>
-    <row r="485" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A485" s="1">
         <v>484</v>
       </c>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="AW485" s="2"/>
     </row>
-    <row r="486" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A486" s="1">
         <v>485</v>
       </c>
@@ -19157,7 +19157,7 @@
       </c>
       <c r="AW486" s="2"/>
     </row>
-    <row r="487" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A487" s="1">
         <v>486</v>
       </c>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="AW487" s="2"/>
     </row>
-    <row r="488" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A488" s="1">
         <v>487</v>
       </c>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="AW488" s="2"/>
     </row>
-    <row r="489" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A489" s="1">
         <v>488</v>
       </c>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="AW489" s="2"/>
     </row>
-    <row r="490" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A490" s="1">
         <v>489</v>
       </c>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="AW490" s="2"/>
     </row>
-    <row r="491" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A491" s="1">
         <v>490</v>
       </c>
@@ -19322,7 +19322,7 @@
       </c>
       <c r="AW491" s="2"/>
     </row>
-    <row r="492" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A492" s="1">
         <v>491</v>
       </c>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="AW492" s="2"/>
     </row>
-    <row r="493" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A493" s="1">
         <v>492</v>
       </c>
@@ -19388,7 +19388,7 @@
       </c>
       <c r="AW493" s="2"/>
     </row>
-    <row r="494" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A494" s="1">
         <v>493</v>
       </c>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="AW494" s="2"/>
     </row>
-    <row r="495" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A495" s="1">
         <v>494</v>
       </c>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="AW495" s="2"/>
     </row>
-    <row r="496" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A496" s="1">
         <v>495</v>
       </c>
@@ -19487,7 +19487,7 @@
       </c>
       <c r="AW496" s="2"/>
     </row>
-    <row r="497" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A497" s="1">
         <v>496</v>
       </c>
@@ -19520,7 +19520,7 @@
       </c>
       <c r="AW497" s="2"/>
     </row>
-    <row r="498" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A498" s="1">
         <v>497</v>
       </c>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="AW498" s="2"/>
     </row>
-    <row r="499" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A499" s="1">
         <v>498</v>
       </c>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="AW499" s="2"/>
     </row>
-    <row r="500" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A500" s="1">
         <v>499</v>
       </c>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="AW500" s="2"/>
     </row>
-    <row r="501" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A501" s="1">
         <v>500</v>
       </c>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="AW501" s="2"/>
     </row>
-    <row r="502" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A502" s="1">
         <v>501</v>
       </c>
@@ -19685,7 +19685,7 @@
       </c>
       <c r="AW502" s="2"/>
     </row>
-    <row r="503" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A503" s="1">
         <v>502</v>
       </c>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="AW503" s="2"/>
     </row>
-    <row r="504" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A504" s="1">
         <v>503</v>
       </c>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="AW504" s="2"/>
     </row>
-    <row r="505" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A505" s="1">
         <v>504</v>
       </c>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="AW505" s="2"/>
     </row>
-    <row r="506" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A506" s="1">
         <v>505</v>
       </c>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="AW506" s="2"/>
     </row>
-    <row r="507" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A507" s="1">
         <v>506</v>
       </c>
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AW507" s="2"/>
     </row>
-    <row r="508" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A508" s="1">
         <v>507</v>
       </c>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="AW508" s="2"/>
     </row>
-    <row r="509" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A509" s="1">
         <v>508</v>
       </c>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="AW509" s="2"/>
     </row>
-    <row r="510" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A510" s="1">
         <v>509</v>
       </c>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="AW510" s="2"/>
     </row>
-    <row r="511" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A511" s="1">
         <v>510</v>
       </c>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="AW511" s="2"/>
     </row>
-    <row r="512" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A512" s="1">
         <v>511</v>
       </c>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="AW512" s="2"/>
     </row>
-    <row r="513" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A513" s="1">
         <v>512</v>
       </c>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="AW513" s="2"/>
     </row>
-    <row r="514" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A514" s="1">
         <v>513</v>
       </c>
@@ -20081,7 +20081,7 @@
       </c>
       <c r="AW514" s="2"/>
     </row>
-    <row r="515" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A515" s="1">
         <v>514</v>
       </c>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="AW515" s="2"/>
     </row>
-    <row r="516" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A516" s="1">
         <v>515</v>
       </c>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="AW516" s="2"/>
     </row>
-    <row r="517" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A517" s="1">
         <v>516</v>
       </c>
@@ -20180,7 +20180,7 @@
       </c>
       <c r="AW517" s="2"/>
     </row>
-    <row r="518" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A518" s="1">
         <v>517</v>
       </c>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="AW518" s="2"/>
     </row>
-    <row r="519" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A519" s="1">
         <v>518</v>
       </c>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="AW519" s="2"/>
     </row>
-    <row r="520" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A520" s="1">
         <v>519</v>
       </c>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AW520" s="2"/>
     </row>
-    <row r="521" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A521" s="1">
         <v>520</v>
       </c>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AW521" s="2"/>
     </row>
-    <row r="522" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A522" s="1">
         <v>521</v>
       </c>
@@ -20345,7 +20345,7 @@
       </c>
       <c r="AW522" s="2"/>
     </row>
-    <row r="523" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A523" s="1">
         <v>522</v>
       </c>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="AW523" s="2"/>
     </row>
-    <row r="524" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A524" s="1">
         <v>523</v>
       </c>
@@ -20411,7 +20411,7 @@
       </c>
       <c r="AW524" s="2"/>
     </row>
-    <row r="525" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A525" s="1">
         <v>524</v>
       </c>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="AW525" s="2"/>
     </row>
-    <row r="526" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A526" s="1">
         <v>525</v>
       </c>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="AW526" s="2"/>
     </row>
-    <row r="527" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A527" s="1">
         <v>526</v>
       </c>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="AW527" s="2"/>
     </row>
-    <row r="528" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A528" s="1">
         <v>527</v>
       </c>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="AW528" s="2"/>
     </row>
-    <row r="529" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A529" s="1">
         <v>528</v>
       </c>
@@ -20576,7 +20576,7 @@
       </c>
       <c r="AW529" s="2"/>
     </row>
-    <row r="530" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A530" s="1">
         <v>529</v>
       </c>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="AW530" s="2"/>
     </row>
-    <row r="531" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A531" s="1">
         <v>530</v>
       </c>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="AW531" s="2"/>
     </row>
-    <row r="532" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A532" s="1">
         <v>531</v>
       </c>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="AW532" s="2"/>
     </row>
-    <row r="533" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A533" s="1">
         <v>532</v>
       </c>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AW533" s="2"/>
     </row>
-    <row r="534" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A534" s="1">
         <v>533</v>
       </c>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="AW534" s="2"/>
     </row>
-    <row r="535" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A535" s="1">
         <v>534</v>
       </c>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="AW535" s="2"/>
     </row>
-    <row r="536" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A536" s="1">
         <v>535</v>
       </c>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="AW536" s="2"/>
     </row>
-    <row r="537" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A537" s="1">
         <v>536</v>
       </c>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="AW537" s="2"/>
     </row>
-    <row r="538" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A538" s="1">
         <v>537</v>
       </c>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="AW538" s="2"/>
     </row>
-    <row r="539" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A539" s="1">
         <v>538</v>
       </c>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AW539" s="2"/>
     </row>
-    <row r="540" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A540" s="1">
         <v>539</v>
       </c>
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AW540" s="2"/>
     </row>
-    <row r="541" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A541" s="1">
         <v>540</v>
       </c>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="AW541" s="2"/>
     </row>
-    <row r="542" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A542" s="1">
         <v>541</v>
       </c>
@@ -21005,7 +21005,7 @@
       </c>
       <c r="AW542" s="2"/>
     </row>
-    <row r="543" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A543" s="1">
         <v>542</v>
       </c>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="AW543" s="2"/>
     </row>
-    <row r="544" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A544" s="1">
         <v>543</v>
       </c>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AW544" s="2"/>
     </row>
-    <row r="545" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A545" s="1">
         <v>544</v>
       </c>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="AW545" s="2"/>
     </row>
-    <row r="546" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A546" s="1">
         <v>545</v>
       </c>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="AW546" s="2"/>
     </row>
-    <row r="547" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A547" s="1">
         <v>546</v>
       </c>
@@ -21170,7 +21170,7 @@
       </c>
       <c r="AW547" s="2"/>
     </row>
-    <row r="548" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A548" s="1">
         <v>547</v>
       </c>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="AW548" s="2"/>
     </row>
-    <row r="549" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A549" s="1">
         <v>548</v>
       </c>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AW549" s="2"/>
     </row>
-    <row r="550" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A550" s="1">
         <v>549</v>
       </c>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="AW550" s="2"/>
     </row>
-    <row r="551" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A551" s="1">
         <v>550</v>
       </c>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="AW551" s="2"/>
     </row>
-    <row r="552" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A552" s="1">
         <v>551</v>
       </c>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="AW552" s="2"/>
     </row>
-    <row r="553" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A553" s="1">
         <v>552</v>
       </c>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="AW553" s="2"/>
     </row>
-    <row r="554" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A554" s="1">
         <v>553</v>
       </c>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="AW554" s="2"/>
     </row>
-    <row r="555" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A555" s="1">
         <v>554</v>
       </c>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AW555" s="2"/>
     </row>
-    <row r="556" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A556" s="1">
         <v>555</v>
       </c>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="AW556" s="2"/>
     </row>
-    <row r="557" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A557" s="1">
         <v>556</v>
       </c>
@@ -21500,7 +21500,7 @@
       </c>
       <c r="AW557" s="2"/>
     </row>
-    <row r="558" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A558" s="1">
         <v>557</v>
       </c>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="AW558" s="2"/>
     </row>
-    <row r="559" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A559" s="1">
         <v>558</v>
       </c>
@@ -21566,7 +21566,7 @@
       </c>
       <c r="AW559" s="2"/>
     </row>
-    <row r="560" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A560" s="1">
         <v>559</v>
       </c>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="AW560" s="2"/>
     </row>
-    <row r="561" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A561" s="1">
         <v>560</v>
       </c>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="AW561" s="2"/>
     </row>
-    <row r="562" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A562" s="1">
         <v>561</v>
       </c>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="AW562" s="2"/>
     </row>
-    <row r="563" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A563" s="1">
         <v>562</v>
       </c>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="AW563" s="2"/>
     </row>
-    <row r="564" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A564" s="1">
         <v>563</v>
       </c>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="AW564" s="2"/>
     </row>
-    <row r="565" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A565" s="1">
         <v>564</v>
       </c>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="AW565" s="2"/>
     </row>
-    <row r="566" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A566" s="1">
         <v>565</v>
       </c>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AW566" s="2"/>
     </row>
-    <row r="567" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A567" s="1">
         <v>566</v>
       </c>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AW567" s="2"/>
     </row>
-    <row r="568" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A568" s="1">
         <v>567</v>
       </c>
@@ -21863,7 +21863,7 @@
       </c>
       <c r="AW568" s="2"/>
     </row>
-    <row r="569" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A569" s="1">
         <v>568</v>
       </c>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="AW569" s="2"/>
     </row>
-    <row r="570" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A570" s="1">
         <v>569</v>
       </c>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AW570" s="2"/>
     </row>
-    <row r="571" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A571" s="1">
         <v>570</v>
       </c>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="AW571" s="2"/>
     </row>
-    <row r="572" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A572" s="1">
         <v>571</v>
       </c>
@@ -21995,7 +21995,7 @@
       </c>
       <c r="AW572" s="2"/>
     </row>
-    <row r="573" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A573" s="1">
         <v>572</v>
       </c>
@@ -22028,7 +22028,7 @@
       </c>
       <c r="AW573" s="2"/>
     </row>
-    <row r="574" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A574" s="1">
         <v>573</v>
       </c>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="AW574" s="2"/>
     </row>
-    <row r="575" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A575" s="1">
         <v>574</v>
       </c>
@@ -22094,7 +22094,7 @@
       </c>
       <c r="AW575" s="2"/>
     </row>
-    <row r="576" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A576" s="1">
         <v>575</v>
       </c>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="AW576" s="2"/>
     </row>
-    <row r="577" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A577" s="1">
         <v>576</v>
       </c>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="AW577" s="2"/>
     </row>
-    <row r="578" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A578" s="1">
         <v>577</v>
       </c>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="AW578" s="2"/>
     </row>
-    <row r="579" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A579" s="1">
         <v>578</v>
       </c>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AW579" s="2"/>
     </row>
-    <row r="580" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A580" s="1">
         <v>579</v>
       </c>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="AW580" s="2"/>
     </row>
-    <row r="581" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A581" s="1">
         <v>580</v>
       </c>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="AW581" s="2"/>
     </row>
-    <row r="582" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A582" s="1">
         <v>581</v>
       </c>
@@ -22325,7 +22325,7 @@
       </c>
       <c r="AW582" s="2"/>
     </row>
-    <row r="583" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A583" s="1">
         <v>582</v>
       </c>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="AW583" s="2"/>
     </row>
-    <row r="584" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A584" s="1">
         <v>583</v>
       </c>
@@ -22391,7 +22391,7 @@
       </c>
       <c r="AW584" s="2"/>
     </row>
-    <row r="585" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A585" s="1">
         <v>584</v>
       </c>
@@ -22424,7 +22424,7 @@
       </c>
       <c r="AW585" s="2"/>
     </row>
-    <row r="586" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A586" s="1">
         <v>585</v>
       </c>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="AW586" s="2"/>
     </row>
-    <row r="587" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A587" s="1">
         <v>586</v>
       </c>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="AW587" s="2"/>
     </row>
-    <row r="588" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A588" s="1">
         <v>587</v>
       </c>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AW588" s="2"/>
     </row>
-    <row r="589" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A589" s="1">
         <v>588</v>
       </c>
@@ -22556,7 +22556,7 @@
       </c>
       <c r="AW589" s="2"/>
     </row>
-    <row r="590" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A590" s="1">
         <v>589</v>
       </c>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="AW590" s="2"/>
     </row>
-    <row r="591" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A591" s="1">
         <v>590</v>
       </c>
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AW591" s="2"/>
     </row>
-    <row r="592" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A592" s="1">
         <v>591</v>
       </c>
@@ -22655,7 +22655,7 @@
       </c>
       <c r="AW592" s="2"/>
     </row>
-    <row r="593" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A593" s="1">
         <v>592</v>
       </c>
@@ -22688,7 +22688,7 @@
       </c>
       <c r="AW593" s="2"/>
     </row>
-    <row r="594" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A594" s="1">
         <v>593</v>
       </c>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="AW594" s="2"/>
     </row>
-    <row r="595" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A595" s="1">
         <v>594</v>
       </c>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="AW595" s="2"/>
     </row>
-    <row r="596" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A596" s="1">
         <v>595</v>
       </c>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="AW596" s="2"/>
     </row>
-    <row r="597" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A597" s="1">
         <v>596</v>
       </c>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="AW597" s="2"/>
     </row>
-    <row r="598" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A598" s="1">
         <v>597</v>
       </c>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="AW598" s="2"/>
     </row>
-    <row r="599" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A599" s="1">
         <v>598</v>
       </c>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="AW599" s="2"/>
     </row>
-    <row r="600" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A600" s="1">
         <v>599</v>
       </c>
@@ -22919,7 +22919,7 @@
       </c>
       <c r="AW600" s="2"/>
     </row>
-    <row r="601" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A601" s="1">
         <v>600</v>
       </c>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AW601" s="2"/>
     </row>
-    <row r="602" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A602" s="1">
         <v>601</v>
       </c>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="AW602" s="2"/>
     </row>
-    <row r="603" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A603" s="1">
         <v>602</v>
       </c>
@@ -23018,7 +23018,7 @@
       </c>
       <c r="AW603" s="2"/>
     </row>
-    <row r="604" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A604" s="1">
         <v>603</v>
       </c>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="AW604" s="2"/>
     </row>
-    <row r="605" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A605" s="1">
         <v>604</v>
       </c>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="AW605" s="2"/>
     </row>
-    <row r="606" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A606" s="1">
         <v>605</v>
       </c>
@@ -23117,7 +23117,7 @@
       </c>
       <c r="AW606" s="2"/>
     </row>
-    <row r="607" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A607" s="1">
         <v>606</v>
       </c>
@@ -23150,7 +23150,7 @@
       </c>
       <c r="AW607" s="2"/>
     </row>
-    <row r="608" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A608" s="1">
         <v>607</v>
       </c>
@@ -23183,7 +23183,7 @@
       </c>
       <c r="AW608" s="2"/>
     </row>
-    <row r="609" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A609" s="1">
         <v>608</v>
       </c>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="AW609" s="2"/>
     </row>
-    <row r="610" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A610" s="1">
         <v>609</v>
       </c>
@@ -23249,7 +23249,7 @@
       </c>
       <c r="AW610" s="2"/>
     </row>
-    <row r="611" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A611" s="1">
         <v>610</v>
       </c>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="AW611" s="2"/>
     </row>
-    <row r="612" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A612" s="1">
         <v>611</v>
       </c>
@@ -23315,7 +23315,7 @@
       </c>
       <c r="AW612" s="2"/>
     </row>
-    <row r="613" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A613" s="1">
         <v>612</v>
       </c>
@@ -23348,7 +23348,7 @@
       </c>
       <c r="AW613" s="2"/>
     </row>
-    <row r="614" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A614" s="1">
         <v>613</v>
       </c>
@@ -23381,7 +23381,7 @@
       </c>
       <c r="AW614" s="2"/>
     </row>
-    <row r="615" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A615" s="1">
         <v>614</v>
       </c>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AW615" s="2"/>
     </row>
-    <row r="616" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A616" s="1">
         <v>615</v>
       </c>
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AW616" s="2"/>
     </row>
-    <row r="617" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A617" s="1">
         <v>616</v>
       </c>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="AW617" s="2"/>
     </row>
-    <row r="618" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A618" s="1">
         <v>617</v>
       </c>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="AW618" s="2"/>
     </row>
-    <row r="619" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A619" s="1">
         <v>618</v>
       </c>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="AW619" s="2"/>
     </row>
-    <row r="620" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A620" s="1">
         <v>619</v>
       </c>
@@ -23579,7 +23579,7 @@
       </c>
       <c r="AW620" s="2"/>
     </row>
-    <row r="621" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A621" s="1">
         <v>620</v>
       </c>
@@ -23612,7 +23612,7 @@
       </c>
       <c r="AW621" s="2"/>
     </row>
-    <row r="622" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A622" s="1">
         <v>621</v>
       </c>
@@ -23645,7 +23645,7 @@
       </c>
       <c r="AW622" s="2"/>
     </row>
-    <row r="623" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A623" s="1">
         <v>622</v>
       </c>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="AW623" s="2"/>
     </row>
-    <row r="624" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A624" s="1">
         <v>623</v>
       </c>
@@ -23711,7 +23711,7 @@
       </c>
       <c r="AW624" s="2"/>
     </row>
-    <row r="625" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A625" s="1">
         <v>624</v>
       </c>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="AW625" s="2"/>
     </row>
-    <row r="626" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A626" s="1">
         <v>625</v>
       </c>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="AW626" s="2"/>
     </row>
-    <row r="627" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A627" s="1">
         <v>626</v>
       </c>
@@ -23810,7 +23810,7 @@
       </c>
       <c r="AW627" s="2"/>
     </row>
-    <row r="628" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A628" s="1">
         <v>627</v>
       </c>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="AW628" s="2"/>
     </row>
-    <row r="629" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A629" s="1">
         <v>628</v>
       </c>
@@ -23876,7 +23876,7 @@
       </c>
       <c r="AW629" s="2"/>
     </row>
-    <row r="630" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A630" s="1">
         <v>629</v>
       </c>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="AW630" s="2"/>
     </row>
-    <row r="631" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A631" s="1">
         <v>630</v>
       </c>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="AW631" s="2"/>
     </row>
-    <row r="632" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A632" s="1">
         <v>631</v>
       </c>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="AW632" s="2"/>
     </row>
-    <row r="633" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A633" s="1">
         <v>632</v>
       </c>
@@ -24008,7 +24008,7 @@
       </c>
       <c r="AW633" s="2"/>
     </row>
-    <row r="634" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A634" s="1">
         <v>633</v>
       </c>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="AW634" s="2"/>
     </row>
-    <row r="635" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A635" s="1">
         <v>634</v>
       </c>
@@ -24074,7 +24074,7 @@
       </c>
       <c r="AW635" s="2"/>
     </row>
-    <row r="636" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A636" s="1">
         <v>635</v>
       </c>
@@ -24107,7 +24107,7 @@
       </c>
       <c r="AW636" s="2"/>
     </row>
-    <row r="637" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A637" s="1">
         <v>636</v>
       </c>
@@ -24140,7 +24140,7 @@
       </c>
       <c r="AW637" s="2"/>
     </row>
-    <row r="638" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A638" s="1">
         <v>637</v>
       </c>
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AW638" s="2"/>
     </row>
-    <row r="639" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A639" s="1">
         <v>638</v>
       </c>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="AW639" s="2"/>
     </row>
-    <row r="640" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A640" s="1">
         <v>639</v>
       </c>
@@ -24239,7 +24239,7 @@
       </c>
       <c r="AW640" s="2"/>
     </row>
-    <row r="641" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A641" s="1">
         <v>640</v>
       </c>
@@ -24272,7 +24272,7 @@
       </c>
       <c r="AW641" s="2"/>
     </row>
-    <row r="642" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A642" s="1">
         <v>641</v>
       </c>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="AW642" s="2"/>
     </row>
-    <row r="643" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A643" s="1">
         <v>642</v>
       </c>
@@ -24338,7 +24338,7 @@
       </c>
       <c r="AW643" s="2"/>
     </row>
-    <row r="644" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A644" s="1">
         <v>643</v>
       </c>
@@ -24371,7 +24371,7 @@
       </c>
       <c r="AW644" s="2"/>
     </row>
-    <row r="645" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A645" s="1">
         <v>644</v>
       </c>
@@ -24404,7 +24404,7 @@
       </c>
       <c r="AW645" s="2"/>
     </row>
-    <row r="646" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A646" s="1">
         <v>645</v>
       </c>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="AW646" s="2"/>
     </row>
-    <row r="647" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A647" s="1">
         <v>646</v>
       </c>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="AW647" s="2"/>
     </row>
-    <row r="648" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A648" s="1">
         <v>647</v>
       </c>
@@ -24503,7 +24503,7 @@
       </c>
       <c r="AW648" s="2"/>
     </row>
-    <row r="649" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A649" s="1">
         <v>648</v>
       </c>
@@ -24536,7 +24536,7 @@
       </c>
       <c r="AW649" s="2"/>
     </row>
-    <row r="650" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A650" s="1">
         <v>649</v>
       </c>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="AW650" s="2"/>
     </row>
-    <row r="651" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A651" s="1">
         <v>650</v>
       </c>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="AW651" s="2"/>
     </row>
-    <row r="652" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A652" s="1">
         <v>651</v>
       </c>
@@ -24635,7 +24635,7 @@
       </c>
       <c r="AW652" s="2"/>
     </row>
-    <row r="653" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A653" s="1">
         <v>652</v>
       </c>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="AW653" s="2"/>
     </row>
-    <row r="654" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A654" s="1">
         <v>653</v>
       </c>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="AW654" s="2"/>
     </row>
-    <row r="655" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A655" s="1">
         <v>654</v>
       </c>
@@ -24734,7 +24734,7 @@
       </c>
       <c r="AW655" s="2"/>
     </row>
-    <row r="656" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A656" s="1">
         <v>655</v>
       </c>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="AW656" s="2"/>
     </row>
-    <row r="657" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A657" s="1">
         <v>656</v>
       </c>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="AW657" s="2"/>
     </row>
-    <row r="658" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A658" s="1">
         <v>657</v>
       </c>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="AW658" s="2"/>
     </row>
-    <row r="659" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A659" s="1">
         <v>658</v>
       </c>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="AW659" s="2"/>
     </row>
-    <row r="660" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A660" s="1">
         <v>659</v>
       </c>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="AW660" s="2"/>
     </row>
-    <row r="661" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A661" s="1">
         <v>660</v>
       </c>
@@ -24932,7 +24932,7 @@
       </c>
       <c r="AW661" s="2"/>
     </row>
-    <row r="662" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A662" s="1">
         <v>661</v>
       </c>
@@ -24965,7 +24965,7 @@
       </c>
       <c r="AW662" s="2"/>
     </row>
-    <row r="663" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A663" s="1">
         <v>662</v>
       </c>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="AW663" s="2"/>
     </row>
-    <row r="664" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A664" s="1">
         <v>663</v>
       </c>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="AW664" s="2"/>
     </row>
-    <row r="665" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A665" s="1">
         <v>664</v>
       </c>
@@ -25064,7 +25064,7 @@
       </c>
       <c r="AW665" s="2"/>
     </row>
-    <row r="666" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A666" s="1">
         <v>665</v>
       </c>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="AW666" s="2"/>
     </row>
-    <row r="667" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A667" s="1">
         <v>666</v>
       </c>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AW667" s="2"/>
     </row>
-    <row r="668" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A668" s="1">
         <v>667</v>
       </c>
@@ -25163,7 +25163,7 @@
       </c>
       <c r="AW668" s="2"/>
     </row>
-    <row r="669" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A669" s="1">
         <v>668</v>
       </c>
@@ -25196,7 +25196,7 @@
       </c>
       <c r="AW669" s="2"/>
     </row>
-    <row r="670" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A670" s="1">
         <v>669</v>
       </c>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="AW670" s="2"/>
     </row>
-    <row r="671" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A671" s="1">
         <v>670</v>
       </c>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="AW671" s="2"/>
     </row>
-    <row r="672" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A672" s="1">
         <v>671</v>
       </c>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="AW672" s="2"/>
     </row>
-    <row r="673" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A673" s="1">
         <v>672</v>
       </c>
@@ -25328,7 +25328,7 @@
       </c>
       <c r="AW673" s="2"/>
     </row>
-    <row r="674" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A674" s="1">
         <v>673</v>
       </c>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="AW674" s="2"/>
     </row>
-    <row r="675" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A675" s="1">
         <v>674</v>
       </c>
@@ -25394,7 +25394,7 @@
       </c>
       <c r="AW675" s="2"/>
     </row>
-    <row r="676" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A676" s="1">
         <v>675</v>
       </c>
@@ -25427,7 +25427,7 @@
       </c>
       <c r="AW676" s="2"/>
     </row>
-    <row r="677" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A677" s="1">
         <v>676</v>
       </c>
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AW677" s="2"/>
     </row>
-    <row r="678" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A678" s="1">
         <v>677</v>
       </c>
@@ -25493,7 +25493,7 @@
       </c>
       <c r="AW678" s="2"/>
     </row>
-    <row r="679" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A679" s="1">
         <v>678</v>
       </c>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AW679" s="2"/>
     </row>
-    <row r="680" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A680" s="1">
         <v>679</v>
       </c>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="AW680" s="2"/>
     </row>
-    <row r="681" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A681" s="1">
         <v>680</v>
       </c>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="AW681" s="2"/>
     </row>
-    <row r="682" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A682" s="1">
         <v>681</v>
       </c>
@@ -25625,7 +25625,7 @@
       </c>
       <c r="AW682" s="2"/>
     </row>
-    <row r="683" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A683" s="1">
         <v>682</v>
       </c>
@@ -25658,7 +25658,7 @@
       </c>
       <c r="AW683" s="2"/>
     </row>
-    <row r="684" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A684" s="1">
         <v>683</v>
       </c>
@@ -25691,7 +25691,7 @@
       </c>
       <c r="AW684" s="2"/>
     </row>
-    <row r="685" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A685" s="1">
         <v>684</v>
       </c>
@@ -25724,7 +25724,7 @@
       </c>
       <c r="AW685" s="2"/>
     </row>
-    <row r="686" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A686" s="1">
         <v>685</v>
       </c>
@@ -25757,7 +25757,7 @@
       </c>
       <c r="AW686" s="2"/>
     </row>
-    <row r="687" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A687" s="1">
         <v>686</v>
       </c>
@@ -25790,7 +25790,7 @@
       </c>
       <c r="AW687" s="2"/>
     </row>
-    <row r="688" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A688" s="1">
         <v>687</v>
       </c>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="AW688" s="2"/>
     </row>
-    <row r="689" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A689" s="1">
         <v>688</v>
       </c>
@@ -25856,7 +25856,7 @@
       </c>
       <c r="AW689" s="2"/>
     </row>
-    <row r="690" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A690" s="1">
         <v>689</v>
       </c>
@@ -25889,7 +25889,7 @@
       </c>
       <c r="AW690" s="2"/>
     </row>
-    <row r="691" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A691" s="1">
         <v>690</v>
       </c>
@@ -25922,7 +25922,7 @@
       </c>
       <c r="AW691" s="2"/>
     </row>
-    <row r="692" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A692" s="1">
         <v>691</v>
       </c>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="AW692" s="2"/>
     </row>
-    <row r="693" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A693" s="1">
         <v>692</v>
       </c>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="AW693" s="2"/>
     </row>
-    <row r="694" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A694" s="1">
         <v>693</v>
       </c>
@@ -26021,7 +26021,7 @@
       </c>
       <c r="AW694" s="2"/>
     </row>
-    <row r="695" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A695" s="1">
         <v>694</v>
       </c>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="AW695" s="2"/>
     </row>
-    <row r="696" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A696" s="1">
         <v>695</v>
       </c>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AW696" s="2"/>
     </row>
-    <row r="697" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A697" s="1">
         <v>696</v>
       </c>
@@ -26120,7 +26120,7 @@
       </c>
       <c r="AW697" s="2"/>
     </row>
-    <row r="698" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A698" s="1">
         <v>697</v>
       </c>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AW698" s="2"/>
     </row>
-    <row r="699" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A699" s="1">
         <v>698</v>
       </c>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="AW699" s="2"/>
     </row>
-    <row r="700" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A700" s="1">
         <v>699</v>
       </c>
@@ -26219,7 +26219,7 @@
       </c>
       <c r="AW700" s="2"/>
     </row>
-    <row r="701" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A701" s="1">
         <v>700</v>
       </c>
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AW701" s="2"/>
     </row>
-    <row r="702" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A702" s="1">
         <v>701</v>
       </c>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="AW702" s="2"/>
     </row>
-    <row r="703" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A703" s="1">
         <v>702</v>
       </c>
@@ -26318,7 +26318,7 @@
       </c>
       <c r="AW703" s="2"/>
     </row>
-    <row r="704" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A704" s="1">
         <v>703</v>
       </c>
@@ -26351,7 +26351,7 @@
       </c>
       <c r="AW704" s="2"/>
     </row>
-    <row r="705" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A705" s="1">
         <v>704</v>
       </c>
@@ -26384,7 +26384,7 @@
       </c>
       <c r="AW705" s="2"/>
     </row>
-    <row r="706" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A706" s="1">
         <v>705</v>
       </c>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="AW706" s="2"/>
     </row>
-    <row r="707" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A707" s="1">
         <v>706</v>
       </c>
@@ -26450,7 +26450,7 @@
       </c>
       <c r="AW707" s="2"/>
     </row>
-    <row r="708" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A708" s="1">
         <v>707</v>
       </c>
@@ -26483,7 +26483,7 @@
       </c>
       <c r="AW708" s="2"/>
     </row>
-    <row r="709" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A709" s="1">
         <v>708</v>
       </c>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="AW709" s="2"/>
     </row>
-    <row r="710" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A710" s="1">
         <v>709</v>
       </c>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="AW710" s="2"/>
     </row>
-    <row r="711" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A711" s="1">
         <v>710</v>
       </c>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="AW711" s="2"/>
     </row>
-    <row r="712" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A712" s="1">
         <v>711</v>
       </c>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="AW712" s="2"/>
     </row>
-    <row r="713" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A713" s="1">
         <v>712</v>
       </c>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AW713" s="2"/>
     </row>
-    <row r="714" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A714" s="1">
         <v>713</v>
       </c>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="AW714" s="2"/>
     </row>
-    <row r="715" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A715" s="1">
         <v>714</v>
       </c>
@@ -26714,7 +26714,7 @@
       </c>
       <c r="AW715" s="2"/>
     </row>
-    <row r="716" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A716" s="1">
         <v>715</v>
       </c>
@@ -26747,7 +26747,7 @@
       </c>
       <c r="AW716" s="2"/>
     </row>
-    <row r="717" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A717" s="1">
         <v>716</v>
       </c>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="AW717" s="2"/>
     </row>
-    <row r="718" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A718" s="1">
         <v>717</v>
       </c>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="AW718" s="2"/>
     </row>
-    <row r="719" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A719" s="1">
         <v>718</v>
       </c>
@@ -26846,7 +26846,7 @@
       </c>
       <c r="AW719" s="2"/>
     </row>
-    <row r="720" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A720" s="1">
         <v>719</v>
       </c>
@@ -26879,7 +26879,7 @@
       </c>
       <c r="AW720" s="2"/>
     </row>
-    <row r="721" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A721" s="1">
         <v>720</v>
       </c>
@@ -26912,7 +26912,7 @@
       </c>
       <c r="AW721" s="2"/>
     </row>
-    <row r="722" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A722" s="1">
         <v>721</v>
       </c>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="AW722" s="2"/>
     </row>
-    <row r="723" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A723" s="1">
         <v>722</v>
       </c>
@@ -26978,7 +26978,7 @@
       </c>
       <c r="AW723" s="2"/>
     </row>
-    <row r="724" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A724" s="1">
         <v>723</v>
       </c>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="AW724" s="2"/>
     </row>
-    <row r="725" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A725" s="1">
         <v>724</v>
       </c>
@@ -27044,7 +27044,7 @@
       </c>
       <c r="AW725" s="2"/>
     </row>
-    <row r="726" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A726" s="1">
         <v>725</v>
       </c>
@@ -27077,7 +27077,7 @@
       </c>
       <c r="AW726" s="2"/>
     </row>
-    <row r="727" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A727" s="1">
         <v>726</v>
       </c>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="AW727" s="2"/>
     </row>
-    <row r="728" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A728" s="1">
         <v>727</v>
       </c>
@@ -27143,7 +27143,7 @@
       </c>
       <c r="AW728" s="2"/>
     </row>
-    <row r="729" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A729" s="1">
         <v>728</v>
       </c>
@@ -27176,7 +27176,7 @@
       </c>
       <c r="AW729" s="2"/>
     </row>
-    <row r="730" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A730" s="1">
         <v>729</v>
       </c>
@@ -27209,7 +27209,7 @@
       </c>
       <c r="AW730" s="2"/>
     </row>
-    <row r="731" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A731" s="1">
         <v>730</v>
       </c>
@@ -27242,7 +27242,7 @@
       </c>
       <c r="AW731" s="2"/>
     </row>
-    <row r="732" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A732" s="1">
         <v>731</v>
       </c>
@@ -27275,7 +27275,7 @@
       </c>
       <c r="AW732" s="2"/>
     </row>
-    <row r="733" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A733" s="1">
         <v>732</v>
       </c>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AW733" s="2"/>
     </row>
-    <row r="734" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A734" s="1">
         <v>733</v>
       </c>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AW734" s="2"/>
     </row>
-    <row r="735" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A735" s="1">
         <v>734</v>
       </c>
@@ -27374,7 +27374,7 @@
       </c>
       <c r="AW735" s="2"/>
     </row>
-    <row r="736" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A736" s="1">
         <v>735</v>
       </c>
@@ -27407,7 +27407,7 @@
       </c>
       <c r="AW736" s="2"/>
     </row>
-    <row r="737" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A737" s="1">
         <v>736</v>
       </c>
@@ -27440,7 +27440,7 @@
       </c>
       <c r="AW737" s="2"/>
     </row>
-    <row r="738" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A738" s="1">
         <v>737</v>
       </c>
@@ -27473,7 +27473,7 @@
       </c>
       <c r="AW738" s="2"/>
     </row>
-    <row r="739" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A739" s="1">
         <v>738</v>
       </c>
@@ -27506,7 +27506,7 @@
       </c>
       <c r="AW739" s="2"/>
     </row>
-    <row r="740" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A740" s="1">
         <v>739</v>
       </c>
@@ -27539,7 +27539,7 @@
       </c>
       <c r="AW740" s="2"/>
     </row>
-    <row r="741" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A741" s="1">
         <v>740</v>
       </c>
@@ -27572,7 +27572,7 @@
       </c>
       <c r="AW741" s="2"/>
     </row>
-    <row r="742" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A742" s="1">
         <v>741</v>
       </c>
@@ -27605,7 +27605,7 @@
       </c>
       <c r="AW742" s="2"/>
     </row>
-    <row r="743" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A743" s="1">
         <v>742</v>
       </c>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="AW743" s="2"/>
     </row>
-    <row r="744" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A744" s="1">
         <v>743</v>
       </c>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="AW744" s="2"/>
     </row>
-    <row r="745" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A745" s="1">
         <v>744</v>
       </c>
@@ -27704,7 +27704,7 @@
       </c>
       <c r="AW745" s="2"/>
     </row>
-    <row r="746" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A746" s="1">
         <v>745</v>
       </c>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="AW746" s="2"/>
     </row>
-    <row r="747" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A747" s="1">
         <v>746</v>
       </c>
@@ -27770,7 +27770,7 @@
       </c>
       <c r="AW747" s="2"/>
     </row>
-    <row r="748" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A748" s="1">
         <v>747</v>
       </c>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="AW748" s="2"/>
     </row>
-    <row r="749" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A749" s="1">
         <v>748</v>
       </c>
@@ -27836,7 +27836,7 @@
       </c>
       <c r="AW749" s="2"/>
     </row>
-    <row r="750" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A750" s="1">
         <v>749</v>
       </c>
@@ -27869,7 +27869,7 @@
       </c>
       <c r="AW750" s="2"/>
     </row>
-    <row r="751" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A751" s="1">
         <v>750</v>
       </c>
@@ -27902,7 +27902,7 @@
       </c>
       <c r="AW751" s="2"/>
     </row>
-    <row r="752" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A752" s="1">
         <v>751</v>
       </c>
@@ -27935,7 +27935,7 @@
       </c>
       <c r="AW752" s="2"/>
     </row>
-    <row r="753" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A753" s="1">
         <v>752</v>
       </c>
@@ -27968,7 +27968,7 @@
       </c>
       <c r="AW753" s="2"/>
     </row>
-    <row r="754" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A754" s="1">
         <v>753</v>
       </c>
@@ -28001,7 +28001,7 @@
       </c>
       <c r="AW754" s="2"/>
     </row>
-    <row r="755" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A755" s="1">
         <v>754</v>
       </c>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AW755" s="2"/>
     </row>
-    <row r="756" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A756" s="1">
         <v>755</v>
       </c>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="AW756" s="2"/>
     </row>
-    <row r="757" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A757" s="1">
         <v>756</v>
       </c>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="AW757" s="2"/>
     </row>
-    <row r="758" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A758" s="1">
         <v>757</v>
       </c>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="AW758" s="2"/>
     </row>
-    <row r="759" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A759" s="1">
         <v>758</v>
       </c>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="AW759" s="2"/>
     </row>
-    <row r="760" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A760" s="1">
         <v>759</v>
       </c>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="AW760" s="2"/>
     </row>
-    <row r="761" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A761" s="1">
         <v>760</v>
       </c>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="AW761" s="2"/>
     </row>
-    <row r="762" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A762" s="1">
         <v>761</v>
       </c>
@@ -28265,7 +28265,7 @@
       </c>
       <c r="AW762" s="2"/>
     </row>
-    <row r="763" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A763" s="1">
         <v>762</v>
       </c>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="AW763" s="2"/>
     </row>
-    <row r="764" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A764" s="1">
         <v>763</v>
       </c>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="AW764" s="2"/>
     </row>
-    <row r="765" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A765" s="1">
         <v>764</v>
       </c>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="AW765" s="2"/>
     </row>
-    <row r="766" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A766" s="1">
         <v>765</v>
       </c>
@@ -28397,7 +28397,7 @@
       </c>
       <c r="AW766" s="2"/>
     </row>
-    <row r="767" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A767" s="1">
         <v>766</v>
       </c>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="AW767" s="2"/>
     </row>
-    <row r="768" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A768" s="1">
         <v>767</v>
       </c>
@@ -28463,7 +28463,7 @@
       </c>
       <c r="AW768" s="2"/>
     </row>
-    <row r="769" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A769" s="1">
         <v>768</v>
       </c>
@@ -28496,7 +28496,7 @@
       </c>
       <c r="AW769" s="2"/>
     </row>
-    <row r="770" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A770" s="1">
         <v>769</v>
       </c>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="AW770" s="2"/>
     </row>
-    <row r="771" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A771" s="1">
         <v>770</v>
       </c>
@@ -28562,7 +28562,7 @@
       </c>
       <c r="AW771" s="2"/>
     </row>
-    <row r="772" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A772" s="1">
         <v>771</v>
       </c>
@@ -28595,7 +28595,7 @@
       </c>
       <c r="AW772" s="2"/>
     </row>
-    <row r="773" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A773" s="1">
         <v>772</v>
       </c>
@@ -28628,7 +28628,7 @@
       </c>
       <c r="AW773" s="2"/>
     </row>
-    <row r="774" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A774" s="1">
         <v>773</v>
       </c>
@@ -28661,7 +28661,7 @@
       </c>
       <c r="AW774" s="2"/>
     </row>
-    <row r="775" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A775" s="1">
         <v>774</v>
       </c>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="AW775" s="2"/>
     </row>
-    <row r="776" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A776" s="1">
         <v>775</v>
       </c>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="AW776" s="2"/>
     </row>
-    <row r="777" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A777" s="1">
         <v>776</v>
       </c>
@@ -28760,7 +28760,7 @@
       </c>
       <c r="AW777" s="2"/>
     </row>
-    <row r="778" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A778" s="1">
         <v>777</v>
       </c>
@@ -28793,7 +28793,7 @@
       </c>
       <c r="AW778" s="2"/>
     </row>
-    <row r="779" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A779" s="1">
         <v>778</v>
       </c>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="AW779" s="2"/>
     </row>
-    <row r="780" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A780" s="1">
         <v>779</v>
       </c>
@@ -28859,7 +28859,7 @@
       </c>
       <c r="AW780" s="2"/>
     </row>
-    <row r="781" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A781" s="1">
         <v>780</v>
       </c>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="AW781" s="2"/>
     </row>
-    <row r="782" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A782" s="1">
         <v>781</v>
       </c>
@@ -28925,7 +28925,7 @@
       </c>
       <c r="AW782" s="2"/>
     </row>
-    <row r="783" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A783" s="1">
         <v>782</v>
       </c>
@@ -28958,7 +28958,7 @@
       </c>
       <c r="AW783" s="2"/>
     </row>
-    <row r="784" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A784" s="1">
         <v>783</v>
       </c>
@@ -28991,7 +28991,7 @@
       </c>
       <c r="AW784" s="2"/>
     </row>
-    <row r="785" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A785" s="1">
         <v>784</v>
       </c>
@@ -29024,7 +29024,7 @@
       </c>
       <c r="AW785" s="2"/>
     </row>
-    <row r="786" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A786" s="1">
         <v>785</v>
       </c>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="AW786" s="2"/>
     </row>
-    <row r="787" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A787" s="1">
         <v>786</v>
       </c>
@@ -29090,7 +29090,7 @@
       </c>
       <c r="AW787" s="2"/>
     </row>
-    <row r="788" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A788" s="1">
         <v>787</v>
       </c>
@@ -29123,7 +29123,7 @@
       </c>
       <c r="AW788" s="2"/>
     </row>
-    <row r="789" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A789" s="1">
         <v>788</v>
       </c>
@@ -29156,7 +29156,7 @@
       </c>
       <c r="AW789" s="2"/>
     </row>
-    <row r="790" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A790" s="1">
         <v>789</v>
       </c>
@@ -29189,7 +29189,7 @@
       </c>
       <c r="AW790" s="2"/>
     </row>
-    <row r="791" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A791" s="1">
         <v>790</v>
       </c>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="AW791" s="2"/>
     </row>
-    <row r="792" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A792" s="1">
         <v>791</v>
       </c>
@@ -29255,7 +29255,7 @@
       </c>
       <c r="AW792" s="2"/>
     </row>
-    <row r="793" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A793" s="1">
         <v>792</v>
       </c>
@@ -29288,7 +29288,7 @@
       </c>
       <c r="AW793" s="2"/>
     </row>
-    <row r="794" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A794" s="1">
         <v>793</v>
       </c>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="AW794" s="2"/>
     </row>
-    <row r="795" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A795" s="1">
         <v>794</v>
       </c>
@@ -29354,7 +29354,7 @@
       </c>
       <c r="AW795" s="2"/>
     </row>
-    <row r="796" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A796" s="1">
         <v>795</v>
       </c>
@@ -29387,7 +29387,7 @@
       </c>
       <c r="AW796" s="2"/>
     </row>
-    <row r="797" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A797" s="1">
         <v>796</v>
       </c>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="AW797" s="2"/>
     </row>
-    <row r="798" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A798" s="1">
         <v>797</v>
       </c>
@@ -29453,7 +29453,7 @@
       </c>
       <c r="AW798" s="2"/>
     </row>
-    <row r="799" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A799" s="1">
         <v>798</v>
       </c>
@@ -29486,7 +29486,7 @@
       </c>
       <c r="AW799" s="2"/>
     </row>
-    <row r="800" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A800" s="1">
         <v>799</v>
       </c>
@@ -29519,7 +29519,7 @@
       </c>
       <c r="AW800" s="2"/>
     </row>
-    <row r="801" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A801" s="1">
         <v>800</v>
       </c>
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AW801" s="2"/>
     </row>
-    <row r="802" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A802" s="1">
         <v>801</v>
       </c>
@@ -29585,7 +29585,7 @@
       </c>
       <c r="AW802" s="2"/>
     </row>
-    <row r="803" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A803" s="1">
         <v>802</v>
       </c>
@@ -29618,7 +29618,7 @@
       </c>
       <c r="AW803" s="2"/>
     </row>
-    <row r="804" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A804" s="1">
         <v>803</v>
       </c>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="AW804" s="2"/>
     </row>
-    <row r="805" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A805" s="1">
         <v>804</v>
       </c>
@@ -29684,7 +29684,7 @@
       </c>
       <c r="AW805" s="2"/>
     </row>
-    <row r="806" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A806" s="1">
         <v>805</v>
       </c>
@@ -29717,7 +29717,7 @@
       </c>
       <c r="AW806" s="2"/>
     </row>
-    <row r="807" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A807" s="1">
         <v>806</v>
       </c>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="AW807" s="2"/>
     </row>
-    <row r="808" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A808" s="1">
         <v>807</v>
       </c>
@@ -29783,7 +29783,7 @@
       </c>
       <c r="AW808" s="2"/>
     </row>
-    <row r="809" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A809" s="1">
         <v>808</v>
       </c>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="AW809" s="2"/>
     </row>
-    <row r="810" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A810" s="1">
         <v>809</v>
       </c>
@@ -29849,7 +29849,7 @@
       </c>
       <c r="AW810" s="2"/>
     </row>
-    <row r="811" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A811" s="1">
         <v>810</v>
       </c>
@@ -29882,7 +29882,7 @@
       </c>
       <c r="AW811" s="2"/>
     </row>
-    <row r="812" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A812" s="1">
         <v>811</v>
       </c>
@@ -29915,7 +29915,7 @@
       </c>
       <c r="AW812" s="2"/>
     </row>
-    <row r="813" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A813" s="1">
         <v>812</v>
       </c>
@@ -29948,7 +29948,7 @@
       </c>
       <c r="AW813" s="2"/>
     </row>
-    <row r="814" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A814" s="1">
         <v>813</v>
       </c>
@@ -29981,7 +29981,7 @@
       </c>
       <c r="AW814" s="2"/>
     </row>
-    <row r="815" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A815" s="1">
         <v>814</v>
       </c>
@@ -30014,7 +30014,7 @@
       </c>
       <c r="AW815" s="2"/>
     </row>
-    <row r="816" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A816" s="1">
         <v>815</v>
       </c>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="AW816" s="2"/>
     </row>
-    <row r="817" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A817" s="1">
         <v>816</v>
       </c>
@@ -30080,7 +30080,7 @@
       </c>
       <c r="AW817" s="2"/>
     </row>
-    <row r="818" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A818" s="1">
         <v>817</v>
       </c>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="AW818" s="2"/>
     </row>
-    <row r="819" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A819" s="1">
         <v>818</v>
       </c>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="AW819" s="2"/>
     </row>
-    <row r="820" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A820" s="1">
         <v>819</v>
       </c>
@@ -30179,7 +30179,7 @@
       </c>
       <c r="AW820" s="2"/>
     </row>
-    <row r="821" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A821" s="1">
         <v>820</v>
       </c>
@@ -30212,7 +30212,7 @@
       </c>
       <c r="AW821" s="2"/>
     </row>
-    <row r="822" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A822" s="1">
         <v>821</v>
       </c>
@@ -30245,7 +30245,7 @@
       </c>
       <c r="AW822" s="2"/>
     </row>
-    <row r="823" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A823" s="1">
         <v>822</v>
       </c>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="AW823" s="2"/>
     </row>
-    <row r="824" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A824" s="1">
         <v>823</v>
       </c>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="AW824" s="2"/>
     </row>
-    <row r="825" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A825" s="1">
         <v>824</v>
       </c>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="AW825" s="2"/>
     </row>
-    <row r="826" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A826" s="1">
         <v>825</v>
       </c>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="AW826" s="2"/>
     </row>
-    <row r="827" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A827" s="1">
         <v>826</v>
       </c>
@@ -30410,7 +30410,7 @@
       </c>
       <c r="AW827" s="2"/>
     </row>
-    <row r="828" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A828" s="1">
         <v>827</v>
       </c>
@@ -30443,7 +30443,7 @@
       </c>
       <c r="AW828" s="2"/>
     </row>
-    <row r="829" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A829" s="1">
         <v>828</v>
       </c>
@@ -30476,7 +30476,7 @@
       </c>
       <c r="AW829" s="2"/>
     </row>
-    <row r="830" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A830" s="1">
         <v>829</v>
       </c>
@@ -30509,7 +30509,7 @@
       </c>
       <c r="AW830" s="2"/>
     </row>
-    <row r="831" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A831" s="1">
         <v>830</v>
       </c>
@@ -30542,7 +30542,7 @@
       </c>
       <c r="AW831" s="2"/>
     </row>
-    <row r="832" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A832" s="1">
         <v>831</v>
       </c>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="AW832" s="2"/>
     </row>
-    <row r="833" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A833" s="1">
         <v>832</v>
       </c>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="AW833" s="2"/>
     </row>
-    <row r="834" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A834" s="1">
         <v>833</v>
       </c>
@@ -30641,7 +30641,7 @@
       </c>
       <c r="AW834" s="2"/>
     </row>
-    <row r="835" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A835" s="1">
         <v>834</v>
       </c>
@@ -30674,7 +30674,7 @@
       </c>
       <c r="AW835" s="2"/>
     </row>
-    <row r="836" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A836" s="1">
         <v>835</v>
       </c>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="AW836" s="2"/>
     </row>
-    <row r="837" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A837" s="1">
         <v>836</v>
       </c>
@@ -30740,7 +30740,7 @@
       </c>
       <c r="AW837" s="2"/>
     </row>
-    <row r="838" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A838" s="1">
         <v>837</v>
       </c>
@@ -30773,7 +30773,7 @@
       </c>
       <c r="AW838" s="2"/>
     </row>
-    <row r="839" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A839" s="1">
         <v>838</v>
       </c>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="AW839" s="2"/>
     </row>
-    <row r="840" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A840" s="1">
         <v>839</v>
       </c>
@@ -30839,7 +30839,7 @@
       </c>
       <c r="AW840" s="2"/>
     </row>
-    <row r="841" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A841" s="1">
         <v>840</v>
       </c>
@@ -30872,7 +30872,7 @@
       </c>
       <c r="AW841" s="2"/>
     </row>
-    <row r="842" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A842" s="1">
         <v>841</v>
       </c>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="AW842" s="2"/>
     </row>
-    <row r="843" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A843" s="1">
         <v>842</v>
       </c>
@@ -30938,7 +30938,7 @@
       </c>
       <c r="AW843" s="2"/>
     </row>
-    <row r="844" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A844" s="1">
         <v>843</v>
       </c>
@@ -30971,7 +30971,7 @@
       </c>
       <c r="AW844" s="2"/>
     </row>
-    <row r="845" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A845" s="1">
         <v>844</v>
       </c>
@@ -31004,7 +31004,7 @@
       </c>
       <c r="AW845" s="2"/>
     </row>
-    <row r="846" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A846" s="1">
         <v>845</v>
       </c>
@@ -31037,7 +31037,7 @@
       </c>
       <c r="AW846" s="2"/>
     </row>
-    <row r="847" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A847" s="1">
         <v>846</v>
       </c>
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AW847" s="2"/>
     </row>
-    <row r="848" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A848" s="1">
         <v>847</v>
       </c>
@@ -31103,7 +31103,7 @@
       </c>
       <c r="AW848" s="2"/>
     </row>
-    <row r="849" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A849" s="1">
         <v>848</v>
       </c>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="AW849" s="2"/>
     </row>
-    <row r="850" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A850" s="1">
         <v>849</v>
       </c>
@@ -31169,7 +31169,7 @@
       </c>
       <c r="AW850" s="2"/>
     </row>
-    <row r="851" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A851" s="1">
         <v>850</v>
       </c>
@@ -31202,7 +31202,7 @@
       </c>
       <c r="AW851" s="2"/>
     </row>
-    <row r="852" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A852" s="1">
         <v>851</v>
       </c>
@@ -31235,7 +31235,7 @@
       </c>
       <c r="AW852" s="2"/>
     </row>
-    <row r="853" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A853" s="1">
         <v>852</v>
       </c>
@@ -31268,7 +31268,7 @@
       </c>
       <c r="AW853" s="2"/>
     </row>
-    <row r="854" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A854" s="1">
         <v>853</v>
       </c>
@@ -31301,7 +31301,7 @@
       </c>
       <c r="AW854" s="2"/>
     </row>
-    <row r="855" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A855" s="1">
         <v>854</v>
       </c>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="AW855" s="2"/>
     </row>
-    <row r="856" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A856" s="1">
         <v>855</v>
       </c>
@@ -31367,7 +31367,7 @@
       </c>
       <c r="AW856" s="2"/>
     </row>
-    <row r="857" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A857" s="1">
         <v>856</v>
       </c>
@@ -31400,7 +31400,7 @@
       </c>
       <c r="AW857" s="2"/>
     </row>
-    <row r="858" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A858" s="1">
         <v>857</v>
       </c>
@@ -31433,7 +31433,7 @@
       </c>
       <c r="AW858" s="2"/>
     </row>
-    <row r="859" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A859" s="1">
         <v>858</v>
       </c>
@@ -31466,7 +31466,7 @@
       </c>
       <c r="AW859" s="2"/>
     </row>
-    <row r="860" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A860" s="1">
         <v>859</v>
       </c>
@@ -31499,7 +31499,7 @@
       </c>
       <c r="AW860" s="2"/>
     </row>
-    <row r="861" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A861" s="1">
         <v>860</v>
       </c>
@@ -31532,7 +31532,7 @@
       </c>
       <c r="AW861" s="2"/>
     </row>
-    <row r="862" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A862" s="1">
         <v>861</v>
       </c>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="AW862" s="2"/>
     </row>
-    <row r="863" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A863" s="1">
         <v>862</v>
       </c>
@@ -31598,7 +31598,7 @@
       </c>
       <c r="AW863" s="2"/>
     </row>
-    <row r="864" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A864" s="1">
         <v>863</v>
       </c>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="AW864" s="2"/>
     </row>
-    <row r="865" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A865" s="1">
         <v>864</v>
       </c>
@@ -31664,7 +31664,7 @@
       </c>
       <c r="AW865" s="2"/>
     </row>
-    <row r="866" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A866" s="1">
         <v>865</v>
       </c>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="AW866" s="2"/>
     </row>
-    <row r="867" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A867" s="1">
         <v>866</v>
       </c>
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AW867" s="2"/>
     </row>
-    <row r="868" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A868" s="1">
         <v>867</v>
       </c>
@@ -31763,7 +31763,7 @@
       </c>
       <c r="AW868" s="2"/>
     </row>
-    <row r="869" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A869" s="1">
         <v>868</v>
       </c>
@@ -31796,7 +31796,7 @@
       </c>
       <c r="AW869" s="2"/>
     </row>
-    <row r="870" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A870" s="1">
         <v>869</v>
       </c>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="AW870" s="2"/>
     </row>
-    <row r="871" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A871" s="1">
         <v>870</v>
       </c>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="AW871" s="2"/>
     </row>
-    <row r="872" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A872" s="1">
         <v>871</v>
       </c>
@@ -31895,7 +31895,7 @@
       </c>
       <c r="AW872" s="2"/>
     </row>
-    <row r="873" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A873" s="1">
         <v>872</v>
       </c>
@@ -31928,7 +31928,7 @@
       </c>
       <c r="AW873" s="2"/>
     </row>
-    <row r="874" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A874" s="1">
         <v>873</v>
       </c>
@@ -31961,7 +31961,7 @@
       </c>
       <c r="AW874" s="2"/>
     </row>
-    <row r="875" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A875" s="1">
         <v>874</v>
       </c>
@@ -31994,7 +31994,7 @@
       </c>
       <c r="AW875" s="2"/>
     </row>
-    <row r="876" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A876" s="1">
         <v>875</v>
       </c>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="AW876" s="2"/>
     </row>
-    <row r="877" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A877" s="1">
         <v>876</v>
       </c>
@@ -32060,7 +32060,7 @@
       </c>
       <c r="AW877" s="2"/>
     </row>
-    <row r="878" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A878" s="1">
         <v>877</v>
       </c>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="AW878" s="2"/>
     </row>
-    <row r="879" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A879" s="1">
         <v>878</v>
       </c>
@@ -32126,7 +32126,7 @@
       </c>
       <c r="AW879" s="2"/>
     </row>
-    <row r="880" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A880" s="1">
         <v>879</v>
       </c>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="AW880" s="2"/>
     </row>
-    <row r="881" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A881" s="1">
         <v>880</v>
       </c>
@@ -32192,7 +32192,7 @@
       </c>
       <c r="AW881" s="2"/>
     </row>
-    <row r="882" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A882" s="1">
         <v>881</v>
       </c>
@@ -32225,7 +32225,7 @@
       </c>
       <c r="AW882" s="2"/>
     </row>
-    <row r="883" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A883" s="1">
         <v>882</v>
       </c>
@@ -32258,7 +32258,7 @@
       </c>
       <c r="AW883" s="2"/>
     </row>
-    <row r="884" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A884" s="1">
         <v>883</v>
       </c>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="AW884" s="2"/>
     </row>
-    <row r="885" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A885" s="1">
         <v>884</v>
       </c>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="AW885" s="2"/>
     </row>
-    <row r="886" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A886" s="1">
         <v>885</v>
       </c>
@@ -32357,7 +32357,7 @@
       </c>
       <c r="AW886" s="2"/>
     </row>
-    <row r="887" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A887" s="1">
         <v>886</v>
       </c>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="AW887" s="2"/>
     </row>
-    <row r="888" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A888" s="1">
         <v>887</v>
       </c>
@@ -32423,7 +32423,7 @@
       </c>
       <c r="AW888" s="2"/>
     </row>
-    <row r="889" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A889" s="1">
         <v>888</v>
       </c>
@@ -32456,7 +32456,7 @@
       </c>
       <c r="AW889" s="2"/>
     </row>
-    <row r="890" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A890" s="1">
         <v>889</v>
       </c>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AW890" s="2"/>
     </row>
-    <row r="891" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A891" s="1">
         <v>890</v>
       </c>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="AW891" s="2"/>
     </row>
-    <row r="892" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A892" s="1">
         <v>891</v>
       </c>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="AW892" s="2"/>
     </row>
-    <row r="893" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A893" s="1">
         <v>892</v>
       </c>
@@ -32588,7 +32588,7 @@
       </c>
       <c r="AW893" s="2"/>
     </row>
-    <row r="894" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A894" s="1">
         <v>893</v>
       </c>
@@ -32621,7 +32621,7 @@
       </c>
       <c r="AW894" s="2"/>
     </row>
-    <row r="895" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A895" s="1">
         <v>894</v>
       </c>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AW895" s="2"/>
     </row>
-    <row r="896" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A896" s="1">
         <v>895</v>
       </c>
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AW896" s="2"/>
     </row>
-    <row r="897" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A897" s="1">
         <v>896</v>
       </c>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="AW897" s="2"/>
     </row>
-    <row r="898" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A898" s="1">
         <v>897</v>
       </c>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="AW898" s="2"/>
     </row>
-    <row r="899" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A899" s="1">
         <v>898</v>
       </c>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="AW899" s="2"/>
     </row>
-    <row r="900" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A900" s="1">
         <v>899</v>
       </c>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="AW900" s="2"/>
     </row>
-    <row r="901" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A901" s="1">
         <v>900</v>
       </c>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="AW901" s="2"/>
     </row>
-    <row r="902" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A902" s="1">
         <v>901</v>
       </c>
@@ -32885,7 +32885,7 @@
       </c>
       <c r="AW902" s="2"/>
     </row>
-    <row r="903" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A903" s="1">
         <v>902</v>
       </c>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="AW903" s="2"/>
     </row>
-    <row r="904" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A904" s="1">
         <v>903</v>
       </c>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="AW904" s="2"/>
     </row>
-    <row r="905" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A905" s="1">
         <v>904</v>
       </c>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="AW905" s="2"/>
     </row>
-    <row r="906" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A906" s="1">
         <v>905</v>
       </c>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="AW906" s="2"/>
     </row>
-    <row r="907" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A907" s="1">
         <v>906</v>
       </c>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="AW907" s="2"/>
     </row>
-    <row r="908" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A908" s="1">
         <v>907</v>
       </c>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="AW908" s="2"/>
     </row>
-    <row r="909" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A909" s="1">
         <v>908</v>
       </c>
@@ -33116,7 +33116,7 @@
       </c>
       <c r="AW909" s="2"/>
     </row>
-    <row r="910" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A910" s="1">
         <v>909</v>
       </c>
@@ -33149,7 +33149,7 @@
       </c>
       <c r="AW910" s="2"/>
     </row>
-    <row r="911" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A911" s="1">
         <v>910</v>
       </c>
@@ -33182,7 +33182,7 @@
       </c>
       <c r="AW911" s="2"/>
     </row>
-    <row r="912" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A912" s="1">
         <v>911</v>
       </c>
@@ -33215,7 +33215,7 @@
       </c>
       <c r="AW912" s="2"/>
     </row>
-    <row r="913" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A913" s="1">
         <v>912</v>
       </c>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="AW913" s="2"/>
     </row>
-    <row r="914" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A914" s="1">
         <v>913</v>
       </c>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="AW914" s="2"/>
     </row>
-    <row r="915" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A915" s="1">
         <v>914</v>
       </c>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="AW915" s="2"/>
     </row>
-    <row r="916" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A916" s="1">
         <v>915</v>
       </c>
@@ -33347,7 +33347,7 @@
       </c>
       <c r="AW916" s="2"/>
     </row>
-    <row r="917" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A917" s="1">
         <v>916</v>
       </c>
@@ -33380,7 +33380,7 @@
       </c>
       <c r="AW917" s="2"/>
     </row>
-    <row r="918" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A918" s="1">
         <v>917</v>
       </c>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="AW918" s="2"/>
     </row>
-    <row r="919" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A919" s="1">
         <v>918</v>
       </c>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="AW919" s="2"/>
     </row>
-    <row r="920" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A920" s="1">
         <v>919</v>
       </c>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="AW920" s="2"/>
     </row>
-    <row r="921" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A921" s="1">
         <v>920</v>
       </c>
@@ -33512,7 +33512,7 @@
       </c>
       <c r="AW921" s="2"/>
     </row>
-    <row r="922" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A922" s="1">
         <v>921</v>
       </c>
@@ -33545,7 +33545,7 @@
       </c>
       <c r="AW922" s="2"/>
     </row>
-    <row r="923" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A923" s="1">
         <v>922</v>
       </c>
@@ -33578,7 +33578,7 @@
       </c>
       <c r="AW923" s="2"/>
     </row>
-    <row r="924" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A924" s="1">
         <v>923</v>
       </c>
@@ -33611,7 +33611,7 @@
       </c>
       <c r="AW924" s="2"/>
     </row>
-    <row r="925" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A925" s="1">
         <v>924</v>
       </c>
@@ -33644,7 +33644,7 @@
       </c>
       <c r="AW925" s="2"/>
     </row>
-    <row r="926" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A926" s="1">
         <v>925</v>
       </c>
@@ -33677,7 +33677,7 @@
       </c>
       <c r="AW926" s="2"/>
     </row>
-    <row r="927" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A927" s="1">
         <v>926</v>
       </c>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="AW927" s="2"/>
     </row>
-    <row r="928" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A928" s="1">
         <v>927</v>
       </c>
@@ -33743,7 +33743,7 @@
       </c>
       <c r="AW928" s="2"/>
     </row>
-    <row r="929" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A929" s="1">
         <v>928</v>
       </c>
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AW929" s="2"/>
     </row>
-    <row r="930" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A930" s="1">
         <v>929</v>
       </c>
@@ -33809,7 +33809,7 @@
       </c>
       <c r="AW930" s="2"/>
     </row>
-    <row r="931" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A931" s="1">
         <v>930</v>
       </c>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="AW931" s="2"/>
     </row>
-    <row r="932" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A932" s="1">
         <v>931</v>
       </c>
@@ -33875,7 +33875,7 @@
       </c>
       <c r="AW932" s="2"/>
     </row>
-    <row r="933" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A933" s="1">
         <v>932</v>
       </c>
@@ -33908,7 +33908,7 @@
       </c>
       <c r="AW933" s="2"/>
     </row>
-    <row r="934" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A934" s="1">
         <v>933</v>
       </c>
@@ -33941,7 +33941,7 @@
       </c>
       <c r="AW934" s="2"/>
     </row>
-    <row r="935" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A935" s="1">
         <v>934</v>
       </c>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AW935" s="2"/>
     </row>
-    <row r="936" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A936" s="1">
         <v>935</v>
       </c>
@@ -34007,7 +34007,7 @@
       </c>
       <c r="AW936" s="2"/>
     </row>
-    <row r="937" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A937" s="1">
         <v>936</v>
       </c>
@@ -34040,7 +34040,7 @@
       </c>
       <c r="AW937" s="2"/>
     </row>
-    <row r="938" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A938" s="1">
         <v>937</v>
       </c>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="AW938" s="2"/>
     </row>
-    <row r="939" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A939" s="1">
         <v>938</v>
       </c>
@@ -34106,7 +34106,7 @@
       </c>
       <c r="AW939" s="2"/>
     </row>
-    <row r="940" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A940" s="1">
         <v>939</v>
       </c>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="AW940" s="2"/>
     </row>
-    <row r="941" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A941" s="1">
         <v>940</v>
       </c>
@@ -34172,7 +34172,7 @@
       </c>
       <c r="AW941" s="2"/>
     </row>
-    <row r="942" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A942" s="1">
         <v>941</v>
       </c>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="AW942" s="2"/>
     </row>
-    <row r="943" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A943" s="1">
         <v>942</v>
       </c>
@@ -34238,7 +34238,7 @@
       </c>
       <c r="AW943" s="2"/>
     </row>
-    <row r="944" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A944" s="1">
         <v>943</v>
       </c>
@@ -34271,7 +34271,7 @@
       </c>
       <c r="AW944" s="2"/>
     </row>
-    <row r="945" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A945" s="1">
         <v>944</v>
       </c>
@@ -34304,7 +34304,7 @@
       </c>
       <c r="AW945" s="2"/>
     </row>
-    <row r="946" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A946" s="1">
         <v>945</v>
       </c>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="AW946" s="2"/>
     </row>
-    <row r="947" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A947" s="1">
         <v>946</v>
       </c>
@@ -34370,7 +34370,7 @@
       </c>
       <c r="AW947" s="2"/>
     </row>
-    <row r="948" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A948" s="1">
         <v>947</v>
       </c>
@@ -34403,7 +34403,7 @@
       </c>
       <c r="AW948" s="2"/>
     </row>
-    <row r="949" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A949" s="1">
         <v>948</v>
       </c>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="AW949" s="2"/>
     </row>
-    <row r="950" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A950" s="1">
         <v>949</v>
       </c>
@@ -34469,7 +34469,7 @@
       </c>
       <c r="AW950" s="2"/>
     </row>
-    <row r="951" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A951" s="1">
         <v>950</v>
       </c>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="AW951" s="2"/>
     </row>
-    <row r="952" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A952" s="1">
         <v>951</v>
       </c>
@@ -34535,7 +34535,7 @@
       </c>
       <c r="AW952" s="2"/>
     </row>
-    <row r="953" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A953" s="1">
         <v>952</v>
       </c>
@@ -34568,7 +34568,7 @@
       </c>
       <c r="AW953" s="2"/>
     </row>
-    <row r="954" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A954" s="1">
         <v>953</v>
       </c>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AW954" s="2"/>
     </row>
-    <row r="955" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A955" s="1">
         <v>954</v>
       </c>
@@ -34634,7 +34634,7 @@
       </c>
       <c r="AW955" s="2"/>
     </row>
-    <row r="956" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A956" s="1">
         <v>955</v>
       </c>
@@ -34667,7 +34667,7 @@
       </c>
       <c r="AW956" s="2"/>
     </row>
-    <row r="957" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A957" s="1">
         <v>956</v>
       </c>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="AW957" s="2"/>
     </row>
-    <row r="958" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A958" s="1">
         <v>957</v>
       </c>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="AW958" s="2"/>
     </row>
-    <row r="959" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A959" s="1">
         <v>958</v>
       </c>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="AW959" s="2"/>
     </row>
-    <row r="960" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A960" s="1">
         <v>959</v>
       </c>
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AW960" s="2"/>
     </row>
-    <row r="961" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A961" s="1">
         <v>960</v>
       </c>
@@ -34832,7 +34832,7 @@
       </c>
       <c r="AW961" s="2"/>
     </row>
-    <row r="962" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A962" s="1">
         <v>961</v>
       </c>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="AW962" s="2"/>
     </row>
-    <row r="963" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A963" s="1">
         <v>962</v>
       </c>
@@ -34898,7 +34898,7 @@
       </c>
       <c r="AW963" s="2"/>
     </row>
-    <row r="964" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A964" s="1">
         <v>963</v>
       </c>
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AW964" s="2"/>
     </row>
-    <row r="965" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A965" s="1">
         <v>964</v>
       </c>
@@ -34964,7 +34964,7 @@
       </c>
       <c r="AW965" s="2"/>
     </row>
-    <row r="966" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A966" s="1">
         <v>965</v>
       </c>
@@ -34997,7 +34997,7 @@
       </c>
       <c r="AW966" s="2"/>
     </row>
-    <row r="967" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A967" s="1">
         <v>966</v>
       </c>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="AW967" s="2"/>
     </row>
-    <row r="968" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A968" s="1">
         <v>967</v>
       </c>
@@ -35063,7 +35063,7 @@
       </c>
       <c r="AW968" s="2"/>
     </row>
-    <row r="969" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A969" s="1">
         <v>968</v>
       </c>
@@ -35096,7 +35096,7 @@
       </c>
       <c r="AW969" s="2"/>
     </row>
-    <row r="970" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A970" s="1">
         <v>969</v>
       </c>
@@ -35129,7 +35129,7 @@
       </c>
       <c r="AW970" s="2"/>
     </row>
-    <row r="971" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A971" s="1">
         <v>970</v>
       </c>
@@ -35162,7 +35162,7 @@
       </c>
       <c r="AW971" s="2"/>
     </row>
-    <row r="972" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A972" s="1">
         <v>971</v>
       </c>
@@ -35195,7 +35195,7 @@
       </c>
       <c r="AW972" s="2"/>
     </row>
-    <row r="973" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A973" s="1">
         <v>972</v>
       </c>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="AW973" s="2"/>
     </row>
-    <row r="974" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A974" s="1">
         <v>973</v>
       </c>
@@ -35261,7 +35261,7 @@
       </c>
       <c r="AW974" s="2"/>
     </row>
-    <row r="975" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A975" s="1">
         <v>974</v>
       </c>
@@ -35294,7 +35294,7 @@
       </c>
       <c r="AW975" s="2"/>
     </row>
-    <row r="976" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A976" s="1">
         <v>975</v>
       </c>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="AW976" s="2"/>
     </row>
-    <row r="977" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A977" s="1">
         <v>976</v>
       </c>
@@ -35360,7 +35360,7 @@
       </c>
       <c r="AW977" s="2"/>
     </row>
-    <row r="978" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A978" s="1">
         <v>977</v>
       </c>
@@ -35393,7 +35393,7 @@
       </c>
       <c r="AW978" s="2"/>
     </row>
-    <row r="979" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A979" s="1">
         <v>978</v>
       </c>
@@ -35426,7 +35426,7 @@
       </c>
       <c r="AW979" s="2"/>
     </row>
-    <row r="980" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A980" s="1">
         <v>979</v>
       </c>
@@ -35459,7 +35459,7 @@
       </c>
       <c r="AW980" s="2"/>
     </row>
-    <row r="981" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A981" s="1">
         <v>980</v>
       </c>
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AW981" s="2"/>
     </row>
-    <row r="982" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A982" s="1">
         <v>981</v>
       </c>
@@ -35525,7 +35525,7 @@
       </c>
       <c r="AW982" s="2"/>
     </row>
-    <row r="983" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A983" s="1">
         <v>982</v>
       </c>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="AW983" s="2"/>
     </row>
-    <row r="984" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A984" s="1">
         <v>983</v>
       </c>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="AW984" s="2"/>
     </row>
-    <row r="985" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A985" s="1">
         <v>984</v>
       </c>
@@ -35624,7 +35624,7 @@
       </c>
       <c r="AW985" s="2"/>
     </row>
-    <row r="986" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A986" s="1">
         <v>985</v>
       </c>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="AW986" s="2"/>
     </row>
-    <row r="987" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A987" s="1">
         <v>986</v>
       </c>
@@ -35690,7 +35690,7 @@
       </c>
       <c r="AW987" s="2"/>
     </row>
-    <row r="988" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A988" s="1">
         <v>987</v>
       </c>
@@ -35723,7 +35723,7 @@
       </c>
       <c r="AW988" s="2"/>
     </row>
-    <row r="989" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A989" s="1">
         <v>988</v>
       </c>
@@ -35756,7 +35756,7 @@
       </c>
       <c r="AW989" s="2"/>
     </row>
-    <row r="990" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A990" s="1">
         <v>989</v>
       </c>
@@ -35789,7 +35789,7 @@
       </c>
       <c r="AW990" s="2"/>
     </row>
-    <row r="991" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A991" s="1">
         <v>990</v>
       </c>
@@ -35822,7 +35822,7 @@
       </c>
       <c r="AW991" s="2"/>
     </row>
-    <row r="992" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A992" s="1">
         <v>991</v>
       </c>
@@ -35855,7 +35855,7 @@
       </c>
       <c r="AW992" s="2"/>
     </row>
-    <row r="993" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A993" s="1">
         <v>992</v>
       </c>
@@ -35888,7 +35888,7 @@
       </c>
       <c r="AW993" s="2"/>
     </row>
-    <row r="994" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A994" s="1">
         <v>993</v>
       </c>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="AW994" s="2"/>
     </row>
-    <row r="995" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A995" s="1">
         <v>994</v>
       </c>
@@ -35954,7 +35954,7 @@
       </c>
       <c r="AW995" s="2"/>
     </row>
-    <row r="996" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A996" s="1">
         <v>995</v>
       </c>
@@ -35987,7 +35987,7 @@
       </c>
       <c r="AW996" s="2"/>
     </row>
-    <row r="997" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A997" s="1">
         <v>996</v>
       </c>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="AW997" s="2"/>
     </row>
-    <row r="998" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A998" s="1">
         <v>997</v>
       </c>
@@ -36053,7 +36053,7 @@
       </c>
       <c r="AW998" s="2"/>
     </row>
-    <row r="999" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A999" s="1">
         <v>998</v>
       </c>
@@ -36086,7 +36086,7 @@
       </c>
       <c r="AW999" s="2"/>
     </row>
-    <row r="1000" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1000" s="1">
         <v>999</v>
       </c>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="AW1000" s="2"/>
     </row>
-    <row r="1001" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1001" s="1">
         <v>1000</v>
       </c>
@@ -36152,7 +36152,7 @@
       </c>
       <c r="AW1001" s="2"/>
     </row>
-    <row r="1002" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1002" s="1">
         <v>1001</v>
       </c>
@@ -36185,7 +36185,7 @@
       </c>
       <c r="AW1002" s="2"/>
     </row>
-    <row r="1003" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1003" s="1">
         <v>1002</v>
       </c>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="AW1003" s="2"/>
     </row>
-    <row r="1004" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1004" s="1">
         <v>1003</v>
       </c>
@@ -36251,7 +36251,7 @@
       </c>
       <c r="AW1004" s="2"/>
     </row>
-    <row r="1005" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1005" s="1">
         <v>1004</v>
       </c>
@@ -36284,7 +36284,7 @@
       </c>
       <c r="AW1005" s="2"/>
     </row>
-    <row r="1006" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1006" s="1">
         <v>1005</v>
       </c>
@@ -36317,7 +36317,7 @@
       </c>
       <c r="AW1006" s="2"/>
     </row>
-    <row r="1007" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1007" s="1">
         <v>1006</v>
       </c>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="AW1007" s="2"/>
     </row>
-    <row r="1008" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1008" s="1">
         <v>1007</v>
       </c>
@@ -36383,7 +36383,7 @@
       </c>
       <c r="AW1008" s="2"/>
     </row>
-    <row r="1009" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1009" s="1">
         <v>1008</v>
       </c>
@@ -36416,7 +36416,7 @@
       </c>
       <c r="AW1009" s="2"/>
     </row>
-    <row r="1010" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1010" s="1">
         <v>1009</v>
       </c>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="AW1010" s="2"/>
     </row>
-    <row r="1011" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1011" s="1">
         <v>1010</v>
       </c>
@@ -36482,7 +36482,7 @@
       </c>
       <c r="AW1011" s="2"/>
     </row>
-    <row r="1012" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1012" s="1">
         <v>1011</v>
       </c>
@@ -36515,7 +36515,7 @@
       </c>
       <c r="AW1012" s="2"/>
     </row>
-    <row r="1013" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1013" s="1">
         <v>1012</v>
       </c>
@@ -36548,7 +36548,7 @@
       </c>
       <c r="AW1013" s="2"/>
     </row>
-    <row r="1014" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1014" s="1">
         <v>1013</v>
       </c>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="AW1014" s="2"/>
     </row>
-    <row r="1015" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1015" s="1">
         <v>1014</v>
       </c>
@@ -36614,7 +36614,7 @@
       </c>
       <c r="AW1015" s="2"/>
     </row>
-    <row r="1016" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1016" s="1">
         <v>1015</v>
       </c>
@@ -36647,7 +36647,7 @@
       </c>
       <c r="AW1016" s="2"/>
     </row>
-    <row r="1017" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1017" s="1">
         <v>1016</v>
       </c>
@@ -36680,7 +36680,7 @@
       </c>
       <c r="AW1017" s="2"/>
     </row>
-    <row r="1018" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1018" s="1">
         <v>1017</v>
       </c>
@@ -36713,7 +36713,7 @@
       </c>
       <c r="AW1018" s="2"/>
     </row>
-    <row r="1019" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1019" s="1">
         <v>1018</v>
       </c>
@@ -36746,7 +36746,7 @@
       </c>
       <c r="AW1019" s="2"/>
     </row>
-    <row r="1020" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1020" s="1">
         <v>1019</v>
       </c>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="AW1020" s="2"/>
     </row>
-    <row r="1021" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1021" s="1">
         <v>1020</v>
       </c>
@@ -36812,7 +36812,7 @@
       </c>
       <c r="AW1021" s="2"/>
     </row>
-    <row r="1022" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1022" s="1">
         <v>1021</v>
       </c>
@@ -36845,7 +36845,7 @@
       </c>
       <c r="AW1022" s="2"/>
     </row>
-    <row r="1023" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1023" s="1">
         <v>1022</v>
       </c>
@@ -36878,7 +36878,7 @@
       </c>
       <c r="AW1023" s="2"/>
     </row>
-    <row r="1024" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1024" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1024" s="1">
         <v>1023</v>
       </c>
@@ -36911,7 +36911,7 @@
       </c>
       <c r="AW1024" s="2"/>
     </row>
-    <row r="1025" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1025" s="1">
         <v>1024</v>
       </c>
@@ -36944,7 +36944,7 @@
       </c>
       <c r="AW1025" s="2"/>
     </row>
-    <row r="1026" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1026" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1026" s="1">
         <v>1025</v>
       </c>
@@ -36977,7 +36977,7 @@
       </c>
       <c r="AW1026" s="2"/>
     </row>
-    <row r="1027" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1027" s="1">
         <v>1026</v>
       </c>
@@ -37010,7 +37010,7 @@
       </c>
       <c r="AW1027" s="2"/>
     </row>
-    <row r="1028" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1028" s="1">
         <v>1027</v>
       </c>
@@ -37043,7 +37043,7 @@
       </c>
       <c r="AW1028" s="2"/>
     </row>
-    <row r="1029" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1029" s="1">
         <v>1028</v>
       </c>
@@ -37076,7 +37076,7 @@
       </c>
       <c r="AW1029" s="2"/>
     </row>
-    <row r="1030" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1030" s="1">
         <v>1029</v>
       </c>
@@ -37109,7 +37109,7 @@
       </c>
       <c r="AW1030" s="2"/>
     </row>
-    <row r="1031" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1031" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1031" s="1">
         <v>1030</v>
       </c>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="AW1031" s="2"/>
     </row>
-    <row r="1032" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1032" s="1">
         <v>1031</v>
       </c>
@@ -37175,7 +37175,7 @@
       </c>
       <c r="AW1032" s="2"/>
     </row>
-    <row r="1033" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1033" s="1">
         <v>1032</v>
       </c>
@@ -37208,7 +37208,7 @@
       </c>
       <c r="AW1033" s="2"/>
     </row>
-    <row r="1034" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1034" s="1">
         <v>1033</v>
       </c>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="AW1034" s="2"/>
     </row>
-    <row r="1035" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1035" s="1">
         <v>1034</v>
       </c>
@@ -37274,7 +37274,7 @@
       </c>
       <c r="AW1035" s="2"/>
     </row>
-    <row r="1036" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1036" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1036" s="1">
         <v>1035</v>
       </c>
@@ -37307,7 +37307,7 @@
       </c>
       <c r="AW1036" s="2"/>
     </row>
-    <row r="1037" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1037" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1037" s="1">
         <v>1036</v>
       </c>
@@ -37340,7 +37340,7 @@
       </c>
       <c r="AW1037" s="2"/>
     </row>
-    <row r="1038" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1038" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1038" s="1">
         <v>1037</v>
       </c>
@@ -37373,7 +37373,7 @@
       </c>
       <c r="AW1038" s="2"/>
     </row>
-    <row r="1039" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1039" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1039" s="1">
         <v>1038</v>
       </c>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="AW1039" s="2"/>
     </row>
-    <row r="1040" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1040" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1040" s="1">
         <v>1039</v>
       </c>
@@ -37439,7 +37439,7 @@
       </c>
       <c r="AW1040" s="2"/>
     </row>
-    <row r="1041" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1041" s="1">
         <v>1040</v>
       </c>
@@ -37472,7 +37472,7 @@
       </c>
       <c r="AW1041" s="2"/>
     </row>
-    <row r="1042" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1042" s="1">
         <v>1041</v>
       </c>
@@ -37505,7 +37505,7 @@
       </c>
       <c r="AW1042" s="2"/>
     </row>
-    <row r="1043" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1043" s="1">
         <v>1042</v>
       </c>
@@ -37538,7 +37538,7 @@
       </c>
       <c r="AW1043" s="2"/>
     </row>
-    <row r="1044" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1044" s="1">
         <v>1043</v>
       </c>
@@ -37571,7 +37571,7 @@
       </c>
       <c r="AW1044" s="2"/>
     </row>
-    <row r="1045" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1045" s="1">
         <v>1044</v>
       </c>
@@ -37604,7 +37604,7 @@
       </c>
       <c r="AW1045" s="2"/>
     </row>
-    <row r="1046" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1046" s="1">
         <v>1045</v>
       </c>
@@ -37637,7 +37637,7 @@
       </c>
       <c r="AW1046" s="2"/>
     </row>
-    <row r="1047" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1047" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1047" s="1">
         <v>1046</v>
       </c>
@@ -37670,7 +37670,7 @@
       </c>
       <c r="AW1047" s="2"/>
     </row>
-    <row r="1048" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1048" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1048" s="1">
         <v>1047</v>
       </c>
@@ -37703,7 +37703,7 @@
       </c>
       <c r="AW1048" s="2"/>
     </row>
-    <row r="1049" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1049" s="1">
         <v>1048</v>
       </c>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="AW1049" s="2"/>
     </row>
-    <row r="1050" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1050" s="1">
         <v>1049</v>
       </c>
@@ -37769,7 +37769,7 @@
       </c>
       <c r="AW1050" s="2"/>
     </row>
-    <row r="1051" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:49" x14ac:dyDescent="0.4">
       <c r="A1051" s="1">
         <v>1050</v>
       </c>
